--- a/8上-下单词表.xlsx
+++ b/8上-下单词表.xlsx
@@ -8222,7 +8222,7 @@
         <v>5</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
@@ -17328,11 +17328,11 @@
         <v>2</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F292" s="1" t="inlineStr">
         <is>
-          <t>café</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="G292" s="1" t="inlineStr">
@@ -17386,11 +17386,11 @@
         <v>2</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F293" s="1" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>honest</t>
         </is>
       </c>
       <c r="G293" s="1" t="inlineStr">
@@ -17425,7 +17425,7 @@
         <v>292</v>
       </c>
       <c r="N293" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" ht="30" customHeight="1">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F294" s="1" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>patient</t>
         </is>
       </c>
       <c r="G294" s="1" t="inlineStr">
@@ -17483,7 +17483,7 @@
         <v>293</v>
       </c>
       <c r="N294" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295" ht="30" customHeight="1">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="F295" s="1" t="inlineStr">
         <is>
-          <t>perfect</t>
+          <t>improve</t>
         </is>
       </c>
       <c r="G295" s="1" t="inlineStr">
@@ -17564,7 +17564,7 @@
       </c>
       <c r="F296" s="1" t="inlineStr">
         <is>
-          <t>mostly</t>
+          <t>confident</t>
         </is>
       </c>
       <c r="G296" s="1" t="inlineStr">
@@ -17599,7 +17599,7 @@
         <v>295</v>
       </c>
       <c r="N296" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297" ht="30" customHeight="1">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="F297" s="1" t="inlineStr">
         <is>
-          <t>receive</t>
+          <t>courage</t>
         </is>
       </c>
       <c r="G297" s="1" t="inlineStr">
@@ -17657,7 +17657,7 @@
         <v>296</v>
       </c>
       <c r="N297" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" ht="30" customHeight="1">
@@ -17680,7 +17680,7 @@
       </c>
       <c r="F298" s="1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>friendship</t>
         </is>
       </c>
       <c r="G298" s="1" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="F299" s="1" t="inlineStr">
         <is>
-          <t>remain</t>
+          <t>admiration</t>
         </is>
       </c>
       <c r="G299" s="1" t="inlineStr">
@@ -17773,7 +17773,7 @@
         <v>298</v>
       </c>
       <c r="N299" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" ht="30" customHeight="1">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="F300" s="1" t="inlineStr">
         <is>
-          <t>lift</t>
+          <t>respect</t>
         </is>
       </c>
       <c r="G300" s="1" t="inlineStr">
@@ -17831,7 +17831,7 @@
         <v>299</v>
       </c>
       <c r="N300" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" ht="30" customHeight="1">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="F301" s="1" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>support</t>
         </is>
       </c>
       <c r="G301" s="1" t="inlineStr">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="F302" s="1" t="inlineStr">
         <is>
-          <t>stair</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="G302" s="1" t="inlineStr">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="F303" s="1" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="G303" s="1" t="inlineStr">
@@ -18005,7 +18005,7 @@
         <v>302</v>
       </c>
       <c r="N303" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" ht="30" customHeight="1">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="F304" s="1" t="inlineStr">
         <is>
-          <t>sightseeing</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="G304" s="1" t="inlineStr">
@@ -18063,7 +18063,7 @@
         <v>303</v>
       </c>
       <c r="N304" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" ht="30" customHeight="1">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="F305" s="1" t="inlineStr">
         <is>
-          <t>imagine</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="G305" s="1" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="F306" s="1" t="inlineStr">
         <is>
-          <t>destination</t>
+          <t>caring</t>
         </is>
       </c>
       <c r="G306" s="1" t="inlineStr">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="F307" s="1" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>describe</t>
         </is>
       </c>
       <c r="G307" s="1" t="inlineStr">
@@ -18260,7 +18260,7 @@
       </c>
       <c r="F308" s="1" t="inlineStr">
         <is>
-          <t>government</t>
+          <t>appearance</t>
         </is>
       </c>
       <c r="G308" s="1" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="F309" s="1" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>straight</t>
         </is>
       </c>
       <c r="G309" s="1" t="inlineStr">
@@ -18353,7 +18353,7 @@
         <v>308</v>
       </c>
       <c r="N309" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310" ht="30" customHeight="1">
@@ -18376,7 +18376,7 @@
       </c>
       <c r="F310" s="1" t="inlineStr">
         <is>
-          <t>endangered</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="G310" s="1" t="inlineStr">
@@ -18411,7 +18411,7 @@
         <v>309</v>
       </c>
       <c r="N310" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311" ht="30" customHeight="1">
@@ -18434,7 +18434,7 @@
       </c>
       <c r="F311" s="1" t="inlineStr">
         <is>
-          <t>stretch</t>
+          <t>same</t>
         </is>
       </c>
       <c r="G311" s="1" t="inlineStr">
@@ -18469,7 +18469,7 @@
         <v>310</v>
       </c>
       <c r="N311" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" ht="30" customHeight="1">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="F312" s="1" t="inlineStr">
         <is>
-          <t>huge</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="G312" s="1" t="inlineStr">
@@ -18550,7 +18550,7 @@
       </c>
       <c r="F313" s="1" t="inlineStr">
         <is>
-          <t>wild</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="G313" s="1" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="F314" s="1" t="inlineStr">
         <is>
-          <t>discover</t>
+          <t>however</t>
         </is>
       </c>
       <c r="G314" s="1" t="inlineStr">
@@ -18643,7 +18643,7 @@
         <v>313</v>
       </c>
       <c r="N314" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" ht="30" customHeight="1">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="F315" s="1" t="inlineStr">
         <is>
-          <t>volcano</t>
+          <t>glad</t>
         </is>
       </c>
       <c r="G315" s="1" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="F316" s="1" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>rise</t>
         </is>
       </c>
       <c r="G316" s="1" t="inlineStr">
@@ -18759,7 +18759,7 @@
         <v>315</v>
       </c>
       <c r="N316" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" ht="30" customHeight="1">
@@ -18782,7 +18782,7 @@
       </c>
       <c r="F317" s="1" t="inlineStr">
         <is>
-          <t>snowmobile</t>
+          <t>end</t>
         </is>
       </c>
       <c r="G317" s="1" t="inlineStr">
@@ -18817,7 +18817,7 @@
         <v>316</v>
       </c>
       <c r="N317" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" ht="30" customHeight="1">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="F318" s="1" t="inlineStr">
         <is>
-          <t>wolf</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="G318" s="1" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="F319" s="1" t="inlineStr">
         <is>
-          <t>branch</t>
+          <t>geography</t>
         </is>
       </c>
       <c r="G319" s="1" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="F320" s="1" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>corner</t>
         </is>
       </c>
       <c r="G320" s="1" t="inlineStr">
@@ -18991,7 +18991,7 @@
         <v>319</v>
       </c>
       <c r="N320" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321" ht="30" customHeight="1">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="F321" s="1" t="inlineStr">
         <is>
-          <t>silent</t>
+          <t>activity</t>
         </is>
       </c>
       <c r="G321" s="1" t="inlineStr">
@@ -19072,7 +19072,7 @@
       </c>
       <c r="F322" s="1" t="inlineStr">
         <is>
-          <t>overlook</t>
+          <t>club</t>
         </is>
       </c>
       <c r="G322" s="1" t="inlineStr">
@@ -19107,7 +19107,7 @@
         <v>321</v>
       </c>
       <c r="N322" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323" ht="30" customHeight="1">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="F323" s="1" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>practise</t>
         </is>
       </c>
       <c r="G323" s="1" t="inlineStr">
@@ -19188,7 +19188,7 @@
       </c>
       <c r="F324" s="1" t="inlineStr">
         <is>
-          <t>oxygen</t>
+          <t>solve</t>
         </is>
       </c>
       <c r="G324" s="1" t="inlineStr">
@@ -19223,7 +19223,7 @@
         <v>323</v>
       </c>
       <c r="N324" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325" ht="30" customHeight="1">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="F325" s="1" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>develop</t>
         </is>
       </c>
       <c r="G325" s="1" t="inlineStr">
@@ -19304,7 +19304,7 @@
       </c>
       <c r="F326" s="1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>skill</t>
         </is>
       </c>
       <c r="G326" s="1" t="inlineStr">
@@ -19339,7 +19339,7 @@
         <v>325</v>
       </c>
       <c r="N326" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" ht="30" customHeight="1">
@@ -19362,7 +19362,7 @@
       </c>
       <c r="F327" s="1" t="inlineStr">
         <is>
-          <t>convenient</t>
+          <t>teen</t>
         </is>
       </c>
       <c r="G327" s="1" t="inlineStr">
@@ -19420,7 +19420,7 @@
       </c>
       <c r="F328" s="1" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>magazine</t>
         </is>
       </c>
       <c r="G328" s="1" t="inlineStr">
@@ -19455,7 +19455,7 @@
         <v>327</v>
       </c>
       <c r="N328" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" ht="30" customHeight="1">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="F329" s="1" t="inlineStr">
         <is>
-          <t>wood</t>
+          <t>teenager</t>
         </is>
       </c>
       <c r="G329" s="1" t="inlineStr">
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F330" s="1" t="inlineStr">
         <is>
-          <t>treat</t>
+          <t>greeting</t>
         </is>
       </c>
       <c r="G330" s="1" t="inlineStr">
@@ -19571,7 +19571,7 @@
         <v>329</v>
       </c>
       <c r="N330" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" ht="30" customHeight="1">
@@ -19594,7 +19594,7 @@
       </c>
       <c r="F331" s="1" t="inlineStr">
         <is>
-          <t>communicate</t>
+          <t>grade</t>
         </is>
       </c>
       <c r="G331" s="1" t="inlineStr">
@@ -19629,7 +19629,7 @@
         <v>330</v>
       </c>
       <c r="N331" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332" ht="30" customHeight="1">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="F332" s="1" t="inlineStr">
         <is>
-          <t>species</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="G332" s="1" t="inlineStr">
@@ -19687,7 +19687,7 @@
         <v>331</v>
       </c>
       <c r="N332" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333" ht="30" customHeight="1">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="F333" s="1" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="G333" s="1" t="inlineStr">
@@ -19745,7 +19745,7 @@
         <v>332</v>
       </c>
       <c r="N333" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" ht="30" customHeight="1">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F334" s="1" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>sincerely</t>
         </is>
       </c>
       <c r="G334" s="1" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="F335" s="1" t="inlineStr">
         <is>
-          <t>borrow</t>
+          <t>diary</t>
         </is>
       </c>
       <c r="G335" s="1" t="inlineStr">
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F336" s="1" t="inlineStr">
         <is>
-          <t>dig</t>
+          <t>project</t>
         </is>
       </c>
       <c r="G336" s="1" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="F337" s="1" t="inlineStr">
         <is>
-          <t>hole</t>
+          <t>poster</t>
         </is>
       </c>
       <c r="G337" s="1" t="inlineStr">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="F338" s="1" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>realize</t>
         </is>
       </c>
       <c r="G338" s="1" t="inlineStr">
@@ -20035,7 +20035,7 @@
         <v>337</v>
       </c>
       <c r="N338" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339" ht="30" customHeight="1">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="F339" s="1" t="inlineStr">
         <is>
-          <t>accident</t>
+          <t>luckily</t>
         </is>
       </c>
       <c r="G339" s="1" t="inlineStr">
@@ -20116,7 +20116,7 @@
       </c>
       <c r="F340" s="1" t="inlineStr">
         <is>
-          <t>knowledge</t>
+          <t>just</t>
         </is>
       </c>
       <c r="G340" s="1" t="inlineStr">
@@ -20170,11 +20170,11 @@
         <v>3</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F341" s="1" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="G341" s="1" t="inlineStr">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="F342" s="1" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>mood</t>
         </is>
       </c>
       <c r="G342" s="1" t="inlineStr">
@@ -20290,7 +20290,7 @@
       </c>
       <c r="F343" s="1" t="inlineStr">
         <is>
-          <t>translation</t>
+          <t>mind</t>
         </is>
       </c>
       <c r="G343" s="1" t="inlineStr">
@@ -20325,7 +20325,7 @@
         <v>342</v>
       </c>
       <c r="N343" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344" ht="30" customHeight="1">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="F344" s="1" t="inlineStr">
         <is>
-          <t>dolphin</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="G344" s="1" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="F345" s="1" t="inlineStr">
         <is>
-          <t>hen</t>
+          <t>celebrate</t>
         </is>
       </c>
       <c r="G345" s="1" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="F346" s="1" t="inlineStr">
         <is>
-          <t>blind</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G346" s="1" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="F347" s="1" t="inlineStr">
         <is>
-          <t>wool</t>
+          <t>rocky</t>
         </is>
       </c>
       <c r="G347" s="1" t="inlineStr">
@@ -20580,7 +20580,7 @@
       </c>
       <c r="F348" s="1" t="inlineStr">
         <is>
-          <t>sir</t>
+          <t>footprint</t>
         </is>
       </c>
       <c r="G348" s="1" t="inlineStr">
@@ -20638,7 +20638,7 @@
       </c>
       <c r="F349" s="1" t="inlineStr">
         <is>
-          <t>receptionist</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="G349" s="1" t="inlineStr">
@@ -20673,7 +20673,7 @@
         <v>348</v>
       </c>
       <c r="N349" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350" ht="30" customHeight="1">
@@ -20696,7 +20696,7 @@
       </c>
       <c r="F350" s="1" t="inlineStr">
         <is>
-          <t>allow</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="G350" s="1" t="inlineStr">
@@ -20731,7 +20731,7 @@
         <v>349</v>
       </c>
       <c r="N350" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351" ht="30" customHeight="1">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="F351" s="1" t="inlineStr">
         <is>
-          <t>apologize</t>
+          <t>sandy</t>
         </is>
       </c>
       <c r="G351" s="1" t="inlineStr">
@@ -20789,7 +20789,7 @@
         <v>350</v>
       </c>
       <c r="N351" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352" ht="30" customHeight="1">
@@ -20812,7 +20812,7 @@
       </c>
       <c r="F352" s="1" t="inlineStr">
         <is>
-          <t>asleep</t>
+          <t>kick</t>
         </is>
       </c>
       <c r="G352" s="1" t="inlineStr">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="F353" s="1" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>town</t>
         </is>
       </c>
       <c r="G353" s="1" t="inlineStr">
@@ -20928,7 +20928,7 @@
       </c>
       <c r="F354" s="1" t="inlineStr">
         <is>
-          <t>fireman</t>
+          <t>feature</t>
         </is>
       </c>
       <c r="G354" s="1" t="inlineStr">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="F355" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>south</t>
         </is>
       </c>
       <c r="G355" s="1" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="F356" s="1" t="inlineStr">
         <is>
-          <t>search-and-rescue</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G356" s="1" t="inlineStr">
@@ -21079,7 +21079,7 @@
         <v>355</v>
       </c>
       <c r="N356" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357" ht="30" customHeight="1">
@@ -21102,7 +21102,7 @@
       </c>
       <c r="F357" s="1" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>loudly</t>
         </is>
       </c>
       <c r="G357" s="1" t="inlineStr">
@@ -21137,7 +21137,7 @@
         <v>356</v>
       </c>
       <c r="N357" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358" ht="30" customHeight="1">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="F358" s="1" t="inlineStr">
         <is>
-          <t>disaster</t>
+          <t>thunder</t>
         </is>
       </c>
       <c r="G358" s="1" t="inlineStr">
@@ -21195,7 +21195,7 @@
         <v>357</v>
       </c>
       <c r="N358" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359" ht="30" customHeight="1">
@@ -21218,7 +21218,7 @@
       </c>
       <c r="F359" s="1" t="inlineStr">
         <is>
-          <t>guest</t>
+          <t>lightning</t>
         </is>
       </c>
       <c r="G359" s="1" t="inlineStr">
@@ -21253,7 +21253,7 @@
         <v>358</v>
       </c>
       <c r="N359" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360" ht="30" customHeight="1">
@@ -21276,7 +21276,7 @@
       </c>
       <c r="F360" s="1" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>fresh</t>
         </is>
       </c>
       <c r="G360" s="1" t="inlineStr">
@@ -21334,7 +21334,7 @@
       </c>
       <c r="F361" s="1" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>gather</t>
         </is>
       </c>
       <c r="G361" s="1" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="F362" s="1" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>peaceful</t>
         </is>
       </c>
       <c r="G362" s="1" t="inlineStr">
@@ -21427,7 +21427,7 @@
         <v>361</v>
       </c>
       <c r="N362" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363" ht="30" customHeight="1">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="F363" s="1" t="inlineStr">
         <is>
-          <t>honey</t>
+          <t>snake</t>
         </is>
       </c>
       <c r="G363" s="1" t="inlineStr">
@@ -21508,7 +21508,7 @@
       </c>
       <c r="F364" s="1" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>through</t>
         </is>
       </c>
       <c r="G364" s="1" t="inlineStr">
@@ -21543,7 +21543,7 @@
         <v>363</v>
       </c>
       <c r="N364" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365" ht="30" customHeight="1">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="F365" s="1" t="inlineStr">
         <is>
-          <t>either</t>
+          <t>part</t>
         </is>
       </c>
       <c r="G365" s="1" t="inlineStr">
@@ -21624,7 +21624,7 @@
       </c>
       <c r="F366" s="1" t="inlineStr">
         <is>
-          <t>shark</t>
+          <t>article</t>
         </is>
       </c>
       <c r="G366" s="1" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="F367" s="1" t="inlineStr">
         <is>
-          <t>scared</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="G367" s="1" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="F368" s="1" t="inlineStr">
         <is>
-          <t>grey</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="G368" s="1" t="inlineStr">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="F369" s="1" t="inlineStr">
         <is>
-          <t>somewhere</t>
+          <t>sandcastle</t>
         </is>
       </c>
       <c r="G369" s="1" t="inlineStr">
@@ -21833,7 +21833,7 @@
         <v>368</v>
       </c>
       <c r="N369" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370" ht="30" customHeight="1">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="F370" s="1" t="inlineStr">
         <is>
-          <t>probably</t>
+          <t>follow</t>
         </is>
       </c>
       <c r="G370" s="1" t="inlineStr">
@@ -21891,7 +21891,7 @@
         <v>369</v>
       </c>
       <c r="N370" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371" ht="30" customHeight="1">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="F371" s="1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>divide</t>
         </is>
       </c>
       <c r="G371" s="1" t="inlineStr">
@@ -21949,7 +21949,7 @@
         <v>370</v>
       </c>
       <c r="N371" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372" ht="30" customHeight="1">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="F372" s="1" t="inlineStr">
         <is>
-          <t>sometime</t>
+          <t>decide</t>
         </is>
       </c>
       <c r="G372" s="1" t="inlineStr">
@@ -22007,7 +22007,7 @@
         <v>371</v>
       </c>
       <c r="N372" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373" ht="30" customHeight="1">
@@ -22030,7 +22030,7 @@
       </c>
       <c r="F373" s="1" t="inlineStr">
         <is>
-          <t>extinct</t>
+          <t>crop</t>
         </is>
       </c>
       <c r="G373" s="1" t="inlineStr">
@@ -22065,7 +22065,7 @@
         <v>372</v>
       </c>
       <c r="N373" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374" ht="30" customHeight="1">
@@ -22088,7 +22088,7 @@
       </c>
       <c r="F374" s="1" t="inlineStr">
         <is>
-          <t>effort</t>
+          <t>culture</t>
         </is>
       </c>
       <c r="G374" s="1" t="inlineStr">
@@ -22123,7 +22123,7 @@
         <v>373</v>
       </c>
       <c r="N374" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375" ht="30" customHeight="1">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="F375" s="1" t="inlineStr">
         <is>
-          <t>everyday</t>
+          <t>local</t>
         </is>
       </c>
       <c r="G375" s="1" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="F376" s="1" t="inlineStr">
         <is>
-          <t>form</t>
+          <t>tradition</t>
         </is>
       </c>
       <c r="G376" s="1" t="inlineStr">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="F377" s="1" t="inlineStr">
         <is>
-          <t>journey</t>
+          <t>continue</t>
         </is>
       </c>
       <c r="G377" s="1" t="inlineStr">
@@ -22320,7 +22320,7 @@
       </c>
       <c r="F378" s="1" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>system</t>
         </is>
       </c>
       <c r="G378" s="1" t="inlineStr">
@@ -22378,7 +22378,7 @@
       </c>
       <c r="F379" s="1" t="inlineStr">
         <is>
-          <t>tap</t>
+          <t>file</t>
         </is>
       </c>
       <c r="G379" s="1" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="F380" s="1" t="inlineStr">
         <is>
-          <t>voice</t>
+          <t>amazing</t>
         </is>
       </c>
       <c r="G380" s="1" t="inlineStr">
@@ -22494,7 +22494,7 @@
       </c>
       <c r="F381" s="1" t="inlineStr">
         <is>
-          <t>eventually</t>
+          <t>planet</t>
         </is>
       </c>
       <c r="G381" s="1" t="inlineStr">
@@ -22529,7 +22529,7 @@
         <v>380</v>
       </c>
       <c r="N381" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382" ht="30" customHeight="1">
@@ -22552,7 +22552,7 @@
       </c>
       <c r="F382" s="1" t="inlineStr">
         <is>
-          <t>pipe</t>
+          <t>billion</t>
         </is>
       </c>
       <c r="G382" s="1" t="inlineStr">
@@ -22587,7 +22587,7 @@
         <v>381</v>
       </c>
       <c r="N382" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383" ht="30" customHeight="1">
@@ -22610,7 +22610,7 @@
       </c>
       <c r="F383" s="1" t="inlineStr">
         <is>
-          <t>return</t>
+          <t>cover</t>
         </is>
       </c>
       <c r="G383" s="1" t="inlineStr">
@@ -22668,7 +22668,7 @@
       </c>
       <c r="F384" s="1" t="inlineStr">
         <is>
-          <t>rush</t>
+          <t>area</t>
         </is>
       </c>
       <c r="G384" s="1" t="inlineStr">
@@ -22726,7 +22726,7 @@
       </c>
       <c r="F385" s="1" t="inlineStr">
         <is>
-          <t>bath</t>
+          <t>freezing</t>
         </is>
       </c>
       <c r="G385" s="1" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="F386" s="1" t="inlineStr">
         <is>
-          <t>salt</t>
+          <t>north</t>
         </is>
       </c>
       <c r="G386" s="1" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="F387" s="1" t="inlineStr">
         <is>
-          <t>brain</t>
+          <t>pole</t>
         </is>
       </c>
       <c r="G387" s="1" t="inlineStr">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="F388" s="1" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>desert</t>
         </is>
       </c>
       <c r="G388" s="1" t="inlineStr">
@@ -22958,7 +22958,7 @@
       </c>
       <c r="F389" s="1" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>metre</t>
         </is>
       </c>
       <c r="G389" s="1" t="inlineStr">
@@ -22993,7 +22993,7 @@
         <v>388</v>
       </c>
       <c r="N389" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390" ht="30" customHeight="1">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="F390" s="1" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>reach</t>
         </is>
       </c>
       <c r="G390" s="1" t="inlineStr">
@@ -23051,7 +23051,7 @@
         <v>389</v>
       </c>
       <c r="N390" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391" ht="30" customHeight="1">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="F391" s="1" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>grain</t>
         </is>
       </c>
       <c r="G391" s="1" t="inlineStr">
@@ -23109,7 +23109,7 @@
         <v>390</v>
       </c>
       <c r="N391" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392" ht="30" customHeight="1">
@@ -23132,7 +23132,7 @@
       </c>
       <c r="F392" s="1" t="inlineStr">
         <is>
-          <t>trade</t>
+          <t>wide</t>
         </is>
       </c>
       <c r="G392" s="1" t="inlineStr">
@@ -23167,7 +23167,7 @@
         <v>391</v>
       </c>
       <c r="N392" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393" ht="30" customHeight="1">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="F393" s="1" t="inlineStr">
         <is>
-          <t>industry</t>
+          <t>whale</t>
         </is>
       </c>
       <c r="G393" s="1" t="inlineStr">
@@ -23225,7 +23225,7 @@
         <v>392</v>
       </c>
       <c r="N393" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394" ht="30" customHeight="1">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="F394" s="1" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>butterfly</t>
         </is>
       </c>
       <c r="G394" s="1" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="F395" s="1" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>provide</t>
         </is>
       </c>
       <c r="G395" s="1" t="inlineStr">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="F396" s="1" t="inlineStr">
         <is>
-          <t>overseas</t>
+          <t>explore</t>
         </is>
       </c>
       <c r="G396" s="1" t="inlineStr">
@@ -23422,7 +23422,7 @@
       </c>
       <c r="F397" s="1" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>disappear</t>
         </is>
       </c>
       <c r="G397" s="1" t="inlineStr">
@@ -23457,7 +23457,7 @@
         <v>396</v>
       </c>
       <c r="N397" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398" ht="30" customHeight="1">
@@ -23480,7 +23480,7 @@
       </c>
       <c r="F398" s="1" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>plastic</t>
         </is>
       </c>
       <c r="G398" s="1" t="inlineStr">
@@ -23515,7 +23515,7 @@
         <v>397</v>
       </c>
       <c r="N398" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399" ht="30" customHeight="1">
@@ -23538,7 +23538,7 @@
       </c>
       <c r="F399" s="1" t="inlineStr">
         <is>
-          <t>nearly</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="G399" s="1" t="inlineStr">
@@ -23573,7 +23573,7 @@
         <v>398</v>
       </c>
       <c r="N399" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400" ht="30" customHeight="1">
@@ -23596,7 +23596,7 @@
       </c>
       <c r="F400" s="1" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>protect</t>
         </is>
       </c>
       <c r="G400" s="1" t="inlineStr">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="F401" s="1" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="G401" s="1" t="inlineStr">
@@ -23689,7 +23689,7 @@
         <v>400</v>
       </c>
       <c r="N401" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402" ht="30" customHeight="1">
@@ -23712,7 +23712,7 @@
       </c>
       <c r="F402" s="1" t="inlineStr">
         <is>
-          <t>throughout</t>
+          <t>groundwater</t>
         </is>
       </c>
       <c r="G402" s="1" t="inlineStr">
@@ -23747,7 +23747,7 @@
         <v>401</v>
       </c>
       <c r="N402" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403" ht="30" customHeight="1">
@@ -23770,7 +23770,7 @@
       </c>
       <c r="F403" s="1" t="inlineStr">
         <is>
-          <t>duty</t>
+          <t>burn</t>
         </is>
       </c>
       <c r="G403" s="1" t="inlineStr">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="F404" s="1" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>oil</t>
         </is>
       </c>
       <c r="G404" s="1" t="inlineStr">
@@ -23863,7 +23863,7 @@
         <v>403</v>
       </c>
       <c r="N404" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405" ht="30" customHeight="1">
@@ -23886,7 +23886,7 @@
       </c>
       <c r="F405" s="1" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="G405" s="1" t="inlineStr">
@@ -23944,7 +23944,7 @@
       </c>
       <c r="F406" s="1" t="inlineStr">
         <is>
-          <t>switch-off</t>
+          <t>harmful</t>
         </is>
       </c>
       <c r="G406" s="1" t="inlineStr">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="F407" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>website</t>
         </is>
       </c>
       <c r="G407" s="1" t="inlineStr">
@@ -24060,7 +24060,7 @@
       </c>
       <c r="F408" s="1" t="inlineStr">
         <is>
-          <t>while</t>
+          <t>own</t>
         </is>
       </c>
       <c r="G408" s="1" t="inlineStr">
@@ -24095,7 +24095,7 @@
         <v>407</v>
       </c>
       <c r="N408" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409" ht="30" customHeight="1">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="F409" s="1" t="inlineStr">
         <is>
-          <t>tablet</t>
+          <t>emperor</t>
         </is>
       </c>
       <c r="G409" s="1" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="F410" s="1" t="inlineStr">
         <is>
-          <t>fridge</t>
+          <t>hunt</t>
         </is>
       </c>
       <c r="G410" s="1" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="F411" s="1" t="inlineStr">
         <is>
-          <t>yogurt</t>
+          <t>war</t>
         </is>
       </c>
       <c r="G411" s="1" t="inlineStr">
@@ -24269,7 +24269,7 @@
         <v>410</v>
       </c>
       <c r="N411" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412" ht="30" customHeight="1">
@@ -24292,7 +24292,7 @@
       </c>
       <c r="F412" s="1" t="inlineStr">
         <is>
-          <t>apartment</t>
+          <t>sandstorm</t>
         </is>
       </c>
       <c r="G412" s="1" t="inlineStr">
@@ -24327,7 +24327,7 @@
         <v>411</v>
       </c>
       <c r="N412" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413" ht="30" customHeight="1">
@@ -24346,11 +24346,11 @@
         <v>6</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F413" s="1" t="inlineStr">
         <is>
-          <t>household</t>
+          <t>solution</t>
         </is>
       </c>
       <c r="G413" s="1" t="inlineStr">
@@ -24408,7 +24408,7 @@
       </c>
       <c r="F414" s="1" t="inlineStr">
         <is>
-          <t>against</t>
+          <t>blow</t>
         </is>
       </c>
       <c r="G414" s="1" t="inlineStr">
@@ -24443,7 +24443,7 @@
         <v>413</v>
       </c>
       <c r="N414" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415" ht="30" customHeight="1">
@@ -24466,7 +24466,7 @@
       </c>
       <c r="F415" s="1" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>generation</t>
         </is>
       </c>
       <c r="G415" s="1" t="inlineStr">
@@ -24501,7 +24501,7 @@
         <v>414</v>
       </c>
       <c r="N415" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416" ht="30" customHeight="1">
@@ -24524,7 +24524,7 @@
       </c>
       <c r="F416" s="1" t="inlineStr">
         <is>
-          <t>safety</t>
+          <t>spacesuit</t>
         </is>
       </c>
       <c r="G416" s="1" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="F417" s="1" t="inlineStr">
         <is>
-          <t>instruction</t>
+          <t>collect</t>
         </is>
       </c>
       <c r="G417" s="1" t="inlineStr">
@@ -24617,7 +24617,7 @@
         <v>416</v>
       </c>
       <c r="N417" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418" ht="30" customHeight="1">
@@ -24640,7 +24640,7 @@
       </c>
       <c r="F418" s="1" t="inlineStr">
         <is>
-          <t>connect</t>
+          <t>leave</t>
         </is>
       </c>
       <c r="G418" s="1" t="inlineStr">
@@ -24698,7 +24698,7 @@
       </c>
       <c r="F419" s="1" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>kilometre</t>
         </is>
       </c>
       <c r="G419" s="1" t="inlineStr">
@@ -24733,7 +24733,7 @@
         <v>418</v>
       </c>
       <c r="N419" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="420" ht="30" customHeight="1">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="F420" s="1" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="G420" s="1" t="inlineStr">
@@ -24814,7 +24814,7 @@
       </c>
       <c r="F421" s="1" t="inlineStr">
         <is>
-          <t>climate</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="G421" s="1" t="inlineStr">
@@ -24849,7 +24849,7 @@
         <v>420</v>
       </c>
       <c r="N421" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422" ht="30" customHeight="1">
@@ -24872,7 +24872,7 @@
       </c>
       <c r="F422" s="1" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G422" s="1" t="inlineStr">
@@ -24907,7 +24907,7 @@
         <v>421</v>
       </c>
       <c r="N422" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423" ht="30" customHeight="1">
@@ -24930,7 +24930,7 @@
       </c>
       <c r="F423" s="1" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>weigh</t>
         </is>
       </c>
       <c r="G423" s="1" t="inlineStr">
@@ -24988,7 +24988,7 @@
       </c>
       <c r="F424" s="1" t="inlineStr">
         <is>
-          <t>television set</t>
+          <t>breathe</t>
         </is>
       </c>
       <c r="G424" s="1" t="inlineStr">
@@ -25023,7 +25023,7 @@
         <v>423</v>
       </c>
       <c r="N424" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425" ht="30" customHeight="1">
@@ -25042,11 +25042,11 @@
         <v>6</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F425" s="1" t="inlineStr">
         <is>
-          <t>landmark</t>
+          <t>facility</t>
         </is>
       </c>
       <c r="G425" s="1" t="inlineStr">
@@ -25081,7 +25081,7 @@
         <v>424</v>
       </c>
       <c r="N425" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426" ht="30" customHeight="1">
@@ -25100,11 +25100,11 @@
         <v>7</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F426" s="1" t="inlineStr">
         <is>
-          <t>contribution</t>
+          <t>adventure</t>
         </is>
       </c>
       <c r="G426" s="1" t="inlineStr">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="F427" s="1" t="inlineStr">
         <is>
-          <t>hero</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="G427" s="1" t="inlineStr">
@@ -25220,7 +25220,7 @@
       </c>
       <c r="F428" s="1" t="inlineStr">
         <is>
-          <t>pioneer</t>
+          <t>experiment</t>
         </is>
       </c>
       <c r="G428" s="1" t="inlineStr">
@@ -25255,7 +25255,7 @@
         <v>427</v>
       </c>
       <c r="N428" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429" ht="30" customHeight="1">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="F429" s="1" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>prepare</t>
         </is>
       </c>
       <c r="G429" s="1" t="inlineStr">
@@ -25336,7 +25336,7 @@
       </c>
       <c r="F430" s="1" t="inlineStr">
         <is>
-          <t>receive</t>
+          <t>dream</t>
         </is>
       </c>
       <c r="G430" s="1" t="inlineStr">
@@ -25371,7 +25371,7 @@
         <v>429</v>
       </c>
       <c r="N430" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431" ht="30" customHeight="1">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="F431" s="1" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="G431" s="1" t="inlineStr">
@@ -25429,7 +25429,7 @@
         <v>430</v>
       </c>
       <c r="N431" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432" ht="30" customHeight="1">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="F432" s="1" t="inlineStr">
         <is>
-          <t>award</t>
+          <t>send</t>
         </is>
       </c>
       <c r="G432" s="1" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="F433" s="1" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="G433" s="1" t="inlineStr">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="F434" s="1" t="inlineStr">
         <is>
-          <t>spend</t>
+          <t>view</t>
         </is>
       </c>
       <c r="G434" s="1" t="inlineStr">
@@ -25626,7 +25626,7 @@
       </c>
       <c r="F435" s="1" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>someday</t>
         </is>
       </c>
       <c r="G435" s="1" t="inlineStr">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="F436" s="1" t="inlineStr">
         <is>
-          <t>achieve</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="G436" s="1" t="inlineStr">
@@ -25719,7 +25719,7 @@
         <v>435</v>
       </c>
       <c r="N436" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437" ht="30" customHeight="1">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="F437" s="1" t="inlineStr">
         <is>
-          <t>well-respected</t>
+          <t>lander</t>
         </is>
       </c>
       <c r="G437" s="1" t="inlineStr">
@@ -25777,7 +25777,7 @@
         <v>436</v>
       </c>
       <c r="N437" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438" ht="30" customHeight="1">
@@ -25800,7 +25800,7 @@
       </c>
       <c r="F438" s="1" t="inlineStr">
         <is>
-          <t>found</t>
+          <t>island</t>
         </is>
       </c>
       <c r="G438" s="1" t="inlineStr">
@@ -25835,7 +25835,7 @@
         <v>437</v>
       </c>
       <c r="N438" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439" ht="30" customHeight="1">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="F439" s="1" t="inlineStr">
         <is>
-          <t>eager</t>
+          <t>ancient</t>
         </is>
       </c>
       <c r="G439" s="1" t="inlineStr">
@@ -25893,7 +25893,7 @@
         <v>438</v>
       </c>
       <c r="N439" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440" ht="30" customHeight="1">
@@ -25916,7 +25916,7 @@
       </c>
       <c r="F440" s="1" t="inlineStr">
         <is>
-          <t>raise</t>
+          <t>poem</t>
         </is>
       </c>
       <c r="G440" s="1" t="inlineStr">
@@ -25974,7 +25974,7 @@
       </c>
       <c r="F441" s="1" t="inlineStr">
         <is>
-          <t>mission</t>
+          <t>express</t>
         </is>
       </c>
       <c r="G441" s="1" t="inlineStr">
@@ -26009,7 +26009,7 @@
         <v>440</v>
       </c>
       <c r="N441" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" ht="30" customHeight="1">
@@ -26028,11 +26028,11 @@
         <v>7</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F442" s="1" t="inlineStr">
         <is>
-          <t>honour</t>
+          <t>determination</t>
         </is>
       </c>
       <c r="G442" s="1" t="inlineStr">
@@ -26090,7 +26090,7 @@
       </c>
       <c r="F443" s="1" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>universe</t>
         </is>
       </c>
       <c r="G443" s="1" t="inlineStr">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="F444" s="1" t="inlineStr">
         <is>
-          <t>approval</t>
+          <t>already</t>
         </is>
       </c>
       <c r="G444" s="1" t="inlineStr">
@@ -26183,7 +26183,7 @@
         <v>443</v>
       </c>
       <c r="N444" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445" ht="30" customHeight="1">
@@ -26206,7 +26206,7 @@
       </c>
       <c r="F445" s="1" t="inlineStr">
         <is>
-          <t>praise</t>
+          <t>century</t>
         </is>
       </c>
       <c r="G445" s="1" t="inlineStr">
@@ -26241,7 +26241,7 @@
         <v>444</v>
       </c>
       <c r="N445" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446" ht="30" customHeight="1">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="F446" s="1" t="inlineStr">
         <is>
-          <t>society</t>
+          <t>neighbour</t>
         </is>
       </c>
       <c r="G446" s="1" t="inlineStr">
@@ -26322,7 +26322,7 @@
       </c>
       <c r="F447" s="1" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>circle</t>
         </is>
       </c>
       <c r="G447" s="1" t="inlineStr">
@@ -26357,7 +26357,7 @@
         <v>446</v>
       </c>
       <c r="N447" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448" ht="30" customHeight="1">
@@ -26380,7 +26380,7 @@
       </c>
       <c r="F448" s="1" t="inlineStr">
         <is>
-          <t>admire</t>
+          <t>surface</t>
         </is>
       </c>
       <c r="G448" s="1" t="inlineStr">
@@ -26438,7 +26438,7 @@
       </c>
       <c r="F449" s="1" t="inlineStr">
         <is>
-          <t>inspire</t>
+          <t>release</t>
         </is>
       </c>
       <c r="G449" s="1" t="inlineStr">
@@ -26496,7 +26496,7 @@
       </c>
       <c r="F450" s="1" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="G450" s="1" t="inlineStr">
@@ -26531,7 +26531,7 @@
         <v>449</v>
       </c>
       <c r="N450" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451" ht="30" customHeight="1">
@@ -26554,7 +26554,7 @@
       </c>
       <c r="F451" s="1" t="inlineStr">
         <is>
-          <t>feed</t>
+          <t>programme</t>
         </is>
       </c>
       <c r="G451" s="1" t="inlineStr">
@@ -26612,7 +26612,7 @@
       </c>
       <c r="F452" s="1" t="inlineStr">
         <is>
-          <t>smokejumper</t>
+          <t>guide</t>
         </is>
       </c>
       <c r="G452" s="1" t="inlineStr">
@@ -26647,7 +26647,7 @@
         <v>451</v>
       </c>
       <c r="N452" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453" ht="30" customHeight="1">
@@ -26670,7 +26670,7 @@
       </c>
       <c r="F453" s="1" t="inlineStr">
         <is>
-          <t>thick</t>
+          <t>east</t>
         </is>
       </c>
       <c r="G453" s="1" t="inlineStr">
@@ -26728,7 +26728,7 @@
       </c>
       <c r="F454" s="1" t="inlineStr">
         <is>
-          <t>certain</t>
+          <t>west</t>
         </is>
       </c>
       <c r="G454" s="1" t="inlineStr">
@@ -26763,7 +26763,7 @@
         <v>453</v>
       </c>
       <c r="N454" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455" ht="30" customHeight="1">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="F455" s="1" t="inlineStr">
         <is>
-          <t>kill</t>
+          <t>mix</t>
         </is>
       </c>
       <c r="G455" s="1" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="F456" s="1" t="inlineStr">
         <is>
-          <t>tool</t>
+          <t>western</t>
         </is>
       </c>
       <c r="G456" s="1" t="inlineStr">
@@ -26902,7 +26902,7 @@
       </c>
       <c r="F457" s="1" t="inlineStr">
         <is>
-          <t>dead</t>
+          <t>style</t>
         </is>
       </c>
       <c r="G457" s="1" t="inlineStr">
@@ -26960,7 +26960,7 @@
       </c>
       <c r="F458" s="1" t="inlineStr">
         <is>
-          <t>brave</t>
+          <t>popular</t>
         </is>
       </c>
       <c r="G458" s="1" t="inlineStr">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="F459" s="1" t="inlineStr">
         <is>
-          <t>tough</t>
+          <t>site</t>
         </is>
       </c>
       <c r="G459" s="1" t="inlineStr">
@@ -27053,7 +27053,7 @@
         <v>458</v>
       </c>
       <c r="N459" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460" ht="30" customHeight="1">
@@ -27076,7 +27076,7 @@
       </c>
       <c r="F460" s="1" t="inlineStr">
         <is>
-          <t>fit</t>
+          <t>across</t>
         </is>
       </c>
       <c r="G460" s="1" t="inlineStr">
@@ -27111,7 +27111,7 @@
         <v>459</v>
       </c>
       <c r="N460" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461" ht="30" customHeight="1">
@@ -27134,7 +27134,7 @@
       </c>
       <c r="F461" s="1" t="inlineStr">
         <is>
-          <t>otherwise</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="G461" s="1" t="inlineStr">
@@ -27169,7 +27169,7 @@
         <v>460</v>
       </c>
       <c r="N461" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462" ht="30" customHeight="1">
@@ -27192,7 +27192,7 @@
       </c>
       <c r="F462" s="1" t="inlineStr">
         <is>
-          <t>survive</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="G462" s="1" t="inlineStr">
@@ -27227,7 +27227,7 @@
         <v>461</v>
       </c>
       <c r="N462" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463" ht="30" customHeight="1">
@@ -27250,7 +27250,7 @@
       </c>
       <c r="F463" s="1" t="inlineStr">
         <is>
-          <t>proud</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="G463" s="1" t="inlineStr">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="F464" s="1" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>design</t>
         </is>
       </c>
       <c r="G464" s="1" t="inlineStr">
@@ -27366,7 +27366,7 @@
       </c>
       <c r="F465" s="1" t="inlineStr">
         <is>
-          <t>athlete</t>
+          <t>else</t>
         </is>
       </c>
       <c r="G465" s="1" t="inlineStr">
@@ -27401,7 +27401,7 @@
         <v>464</v>
       </c>
       <c r="N465" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466" ht="30" customHeight="1">
@@ -27424,7 +27424,7 @@
       </c>
       <c r="F466" s="1" t="inlineStr">
         <is>
-          <t>biologist</t>
+          <t>suggestion</t>
         </is>
       </c>
       <c r="G466" s="1" t="inlineStr">
@@ -27459,7 +27459,7 @@
         <v>465</v>
       </c>
       <c r="N466" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467" ht="30" customHeight="1">
@@ -27482,7 +27482,7 @@
       </c>
       <c r="F467" s="1" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>tip</t>
         </is>
       </c>
       <c r="G467" s="1" t="inlineStr">
@@ -27517,7 +27517,7 @@
         <v>466</v>
       </c>
       <c r="N467" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468" ht="30" customHeight="1">
@@ -27540,7 +27540,7 @@
       </c>
       <c r="F468" s="1" t="inlineStr">
         <is>
-          <t>interest</t>
+          <t>historic</t>
         </is>
       </c>
       <c r="G468" s="1" t="inlineStr">
@@ -27598,7 +27598,7 @@
       </c>
       <c r="F469" s="1" t="inlineStr">
         <is>
-          <t>career</t>
+          <t>list</t>
         </is>
       </c>
       <c r="G469" s="1" t="inlineStr">
@@ -27633,7 +27633,7 @@
         <v>468</v>
       </c>
       <c r="N469" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470" ht="30" customHeight="1">
@@ -27656,7 +27656,7 @@
       </c>
       <c r="F470" s="1" t="inlineStr">
         <is>
-          <t>lifetime</t>
+          <t>landscape</t>
         </is>
       </c>
       <c r="G470" s="1" t="inlineStr">
@@ -27714,7 +27714,7 @@
       </c>
       <c r="F471" s="1" t="inlineStr">
         <is>
-          <t>diamond</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="G471" s="1" t="inlineStr">
@@ -27749,7 +27749,7 @@
         <v>470</v>
       </c>
       <c r="N471" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472" ht="30" customHeight="1">
@@ -27772,7 +27772,7 @@
       </c>
       <c r="F472" s="1" t="inlineStr">
         <is>
-          <t>belt</t>
+          <t>general</t>
         </is>
       </c>
       <c r="G472" s="1" t="inlineStr">
@@ -27807,7 +27807,7 @@
         <v>471</v>
       </c>
       <c r="N472" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473" ht="30" customHeight="1">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="F473" s="1" t="inlineStr">
         <is>
-          <t>shoot</t>
+          <t>sight</t>
         </is>
       </c>
       <c r="G473" s="1" t="inlineStr">
@@ -27865,7 +27865,7 @@
         <v>472</v>
       </c>
       <c r="N473" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474" ht="30" customHeight="1">
@@ -27888,7 +27888,7 @@
       </c>
       <c r="F474" s="1" t="inlineStr">
         <is>
-          <t>extremely</t>
+          <t>natural</t>
         </is>
       </c>
       <c r="G474" s="1" t="inlineStr">
@@ -27923,7 +27923,7 @@
         <v>473</v>
       </c>
       <c r="N474" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475" ht="30" customHeight="1">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="F475" s="1" t="inlineStr">
         <is>
-          <t>curious</t>
+          <t>almost</t>
         </is>
       </c>
       <c r="G475" s="1" t="inlineStr">
@@ -27981,7 +27981,7 @@
         <v>474</v>
       </c>
       <c r="N475" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476" ht="30" customHeight="1">
@@ -28004,7 +28004,7 @@
       </c>
       <c r="F476" s="1" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>become</t>
         </is>
       </c>
       <c r="G476" s="1" t="inlineStr">
@@ -28039,7 +28039,7 @@
         <v>475</v>
       </c>
       <c r="N476" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477" ht="30" customHeight="1">
@@ -28062,7 +28062,7 @@
       </c>
       <c r="F477" s="1" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>gateway</t>
         </is>
       </c>
       <c r="G477" s="1" t="inlineStr">
@@ -28097,7 +28097,7 @@
         <v>476</v>
       </c>
       <c r="N477" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478" ht="30" customHeight="1">
@@ -28120,7 +28120,7 @@
       </c>
       <c r="F478" s="1" t="inlineStr">
         <is>
-          <t>beyond</t>
+          <t>influence</t>
         </is>
       </c>
       <c r="G478" s="1" t="inlineStr">
@@ -28178,7 +28178,7 @@
       </c>
       <c r="F479" s="1" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>artwork</t>
         </is>
       </c>
       <c r="G479" s="1" t="inlineStr">
@@ -28213,7 +28213,7 @@
         <v>478</v>
       </c>
       <c r="N479" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480" ht="30" customHeight="1">
@@ -28236,7 +28236,7 @@
       </c>
       <c r="F480" s="1" t="inlineStr">
         <is>
-          <t>lively</t>
+          <t>painting</t>
         </is>
       </c>
       <c r="G480" s="1" t="inlineStr">
@@ -28271,7 +28271,7 @@
         <v>479</v>
       </c>
       <c r="N480" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481" ht="30" customHeight="1">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="F481" s="1" t="inlineStr">
         <is>
-          <t>actually</t>
+          <t>scene</t>
         </is>
       </c>
       <c r="G481" s="1" t="inlineStr">
@@ -28329,7 +28329,7 @@
         <v>480</v>
       </c>
       <c r="N481" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482" ht="30" customHeight="1">
@@ -28352,7 +28352,7 @@
       </c>
       <c r="F482" s="1" t="inlineStr">
         <is>
-          <t>sail</t>
+          <t>wife</t>
         </is>
       </c>
       <c r="G482" s="1" t="inlineStr">
@@ -28387,7 +28387,7 @@
         <v>481</v>
       </c>
       <c r="N482" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483" ht="30" customHeight="1">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="F483" s="1" t="inlineStr">
         <is>
-          <t>ability</t>
+          <t>stone</t>
         </is>
       </c>
       <c r="G483" s="1" t="inlineStr">
@@ -28464,11 +28464,11 @@
         <v>8</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F484" s="1" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="G484" s="1" t="inlineStr">
@@ -28526,7 +28526,7 @@
       </c>
       <c r="F485" s="1" t="inlineStr">
         <is>
-          <t>perform</t>
+          <t>literature</t>
         </is>
       </c>
       <c r="G485" s="1" t="inlineStr">
@@ -28561,7 +28561,7 @@
         <v>484</v>
       </c>
       <c r="N485" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="486" ht="30" customHeight="1">
@@ -28584,7 +28584,7 @@
       </c>
       <c r="F486" s="1" t="inlineStr">
         <is>
-          <t>kiss</t>
+          <t>act</t>
         </is>
       </c>
       <c r="G486" s="1" t="inlineStr">
@@ -28642,7 +28642,7 @@
       </c>
       <c r="F487" s="1" t="inlineStr">
         <is>
-          <t>hug</t>
+          <t>appreciate</t>
         </is>
       </c>
       <c r="G487" s="1" t="inlineStr">
@@ -28677,7 +28677,7 @@
         <v>486</v>
       </c>
       <c r="N487" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488" ht="30" customHeight="1">
@@ -28700,7 +28700,7 @@
       </c>
       <c r="F488" s="1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>join</t>
         </is>
       </c>
       <c r="G488" s="1" t="inlineStr">
@@ -28735,7 +28735,7 @@
         <v>487</v>
       </c>
       <c r="N488" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489" ht="30" customHeight="1">
@@ -28754,11 +28754,11 @@
         <v>8</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F489" s="1" t="inlineStr">
         <is>
-          <t>compare</t>
+          <t>definitely</t>
         </is>
       </c>
       <c r="G489" s="1" t="inlineStr">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="F490" s="1" t="inlineStr">
         <is>
-          <t>nowadays</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="G490" s="1" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="F491" s="1" t="inlineStr">
         <is>
-          <t>human being</t>
+          <t>rocket</t>
         </is>
       </c>
       <c r="G491" s="1" t="inlineStr">
@@ -28932,7 +28932,7 @@
       </c>
       <c r="F492" s="1" t="inlineStr">
         <is>
-          <t>lecture</t>
+          <t>launch</t>
         </is>
       </c>
       <c r="G492" s="1" t="inlineStr">
@@ -28967,7 +28967,7 @@
         <v>491</v>
       </c>
       <c r="N492" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="493" ht="30" customHeight="1">
@@ -28990,7 +28990,7 @@
       </c>
       <c r="F493" s="1" t="inlineStr">
         <is>
-          <t>dinosaur</t>
+          <t>shout</t>
         </is>
       </c>
       <c r="G493" s="1" t="inlineStr">
@@ -29044,7 +29044,7 @@
       </c>
       <c r="F494" s="1" t="inlineStr">
         <is>
-          <t>intelligent</t>
+          <t>power</t>
         </is>
       </c>
       <c r="G494" s="1" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="F495" s="1" t="inlineStr">
         <is>
-          <t>talented</t>
+          <t>moment</t>
         </is>
       </c>
       <c r="G495" s="1" t="inlineStr">
@@ -29160,7 +29160,7 @@
       </c>
       <c r="F496" s="1" t="inlineStr">
         <is>
-          <t>artistic</t>
+          <t>member</t>
         </is>
       </c>
       <c r="G496" s="1" t="inlineStr">
@@ -29218,7 +29218,7 @@
       </c>
       <c r="F497" s="1" t="inlineStr">
         <is>
-          <t>perhaps</t>
+          <t>shape</t>
         </is>
       </c>
       <c r="G497" s="1" t="inlineStr">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="F498" s="1" t="inlineStr">
         <is>
-          <t>notebook</t>
+          <t>hike</t>
         </is>
       </c>
       <c r="G498" s="1" t="inlineStr">
@@ -29334,7 +29334,7 @@
       </c>
       <c r="F499" s="1" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>recently</t>
         </is>
       </c>
       <c r="G499" s="1" t="inlineStr">
@@ -29369,7 +29369,7 @@
         <v>498</v>
       </c>
       <c r="N499" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500" ht="30" customHeight="1">
@@ -29392,7 +29392,7 @@
       </c>
       <c r="F500" s="1" t="inlineStr">
         <is>
-          <t>prehistoric</t>
+          <t>attend</t>
         </is>
       </c>
       <c r="G500" s="1" t="inlineStr">
@@ -29427,7 +29427,7 @@
         <v>499</v>
       </c>
       <c r="N500" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="501" ht="30" customHeight="1">
@@ -29450,7 +29450,7 @@
       </c>
       <c r="F501" s="1" t="inlineStr">
         <is>
-          <t>completely</t>
+          <t>charity</t>
         </is>
       </c>
       <c r="G501" s="1" t="inlineStr">
@@ -29485,7 +29485,7 @@
         <v>500</v>
       </c>
       <c r="N501" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502" ht="30" customHeight="1">
@@ -29508,7 +29508,7 @@
       </c>
       <c r="F502" s="1" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>sale</t>
         </is>
       </c>
       <c r="G502" s="1" t="inlineStr">
@@ -29566,7 +29566,7 @@
       </c>
       <c r="F503" s="1" t="inlineStr">
         <is>
-          <t>birth</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="G503" s="1" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="F504" s="1" t="inlineStr">
         <is>
-          <t>suffering</t>
+          <t>decorate</t>
         </is>
       </c>
       <c r="G504" s="1" t="inlineStr">
@@ -29682,7 +29682,7 @@
       </c>
       <c r="F505" s="1" t="inlineStr">
         <is>
-          <t>artist</t>
+          <t>difference</t>
         </is>
       </c>
       <c r="G505" s="1" t="inlineStr">
@@ -29740,7 +29740,7 @@
       </c>
       <c r="F506" s="1" t="inlineStr">
         <is>
-          <t>piece</t>
+          <t>compete</t>
         </is>
       </c>
       <c r="G506" s="1" t="inlineStr">
@@ -29775,7 +29775,7 @@
         <v>505</v>
       </c>
       <c r="N506" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507" ht="30" customHeight="1">
@@ -29798,7 +29798,7 @@
       </c>
       <c r="F507" s="1" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>event</t>
         </is>
       </c>
       <c r="G507" s="1" t="inlineStr">
@@ -29856,7 +29856,7 @@
       </c>
       <c r="F508" s="1" t="inlineStr">
         <is>
-          <t>whole</t>
+          <t>spoon</t>
         </is>
       </c>
       <c r="G508" s="1" t="inlineStr">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="F509" s="1" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="G509" s="1" t="inlineStr">
@@ -29949,7 +29949,7 @@
         <v>508</v>
       </c>
       <c r="N509" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510" ht="30" customHeight="1">
@@ -29972,7 +29972,7 @@
       </c>
       <c r="F510" s="1" t="inlineStr">
         <is>
-          <t>organize</t>
+          <t>fantastic</t>
         </is>
       </c>
       <c r="G510" s="1" t="inlineStr">
@@ -30007,7 +30007,7 @@
         <v>509</v>
       </c>
       <c r="N510" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511" ht="30" customHeight="1">
@@ -30030,7 +30030,7 @@
       </c>
       <c r="F511" s="1" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>dollar</t>
         </is>
       </c>
       <c r="G511" s="1" t="inlineStr">
@@ -30065,7 +30065,7 @@
         <v>510</v>
       </c>
       <c r="N511" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512" ht="30" customHeight="1">
@@ -30088,7 +30088,7 @@
       </c>
       <c r="F512" s="1" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>pie</t>
         </is>
       </c>
       <c r="G512" s="1" t="inlineStr">
@@ -30146,7 +30146,7 @@
       </c>
       <c r="F513" s="1" t="inlineStr">
         <is>
-          <t>die out</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="G513" s="1" t="inlineStr">
@@ -30181,7 +30181,7 @@
         <v>512</v>
       </c>
       <c r="N513" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514" ht="30" customHeight="1">
@@ -30204,7 +30204,7 @@
       </c>
       <c r="F514" s="1" t="inlineStr">
         <is>
-          <t>a type of</t>
+          <t>ring</t>
         </is>
       </c>
       <c r="G514" s="1" t="inlineStr">
@@ -30239,7 +30239,7 @@
         <v>513</v>
       </c>
       <c r="N514" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515" ht="30" customHeight="1">
@@ -30262,7 +30262,7 @@
       </c>
       <c r="F515" s="1" t="inlineStr">
         <is>
-          <t>be related to</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="G515" s="1" t="inlineStr">
@@ -30297,7 +30297,7 @@
         <v>514</v>
       </c>
       <c r="N515" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="516" ht="30" customHeight="1">
@@ -30320,7 +30320,7 @@
       </c>
       <c r="F516" s="1" t="inlineStr">
         <is>
-          <t>general education</t>
+          <t>own</t>
         </is>
       </c>
       <c r="G516" s="1" t="inlineStr">
@@ -30355,7 +30355,7 @@
         <v>515</v>
       </c>
       <c r="N516" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517" ht="30" customHeight="1">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="F517" s="1" t="inlineStr">
         <is>
-          <t>go back a long way</t>
+          <t>valuable</t>
         </is>
       </c>
       <c r="G517" s="1" t="inlineStr">
@@ -30413,7 +30413,7 @@
         <v>516</v>
       </c>
       <c r="N517" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="518" ht="30" customHeight="1">
@@ -30436,7 +30436,7 @@
       </c>
       <c r="F518" s="1" t="inlineStr">
         <is>
-          <t>be similar to</t>
+          <t>handle</t>
         </is>
       </c>
       <c r="G518" s="1" t="inlineStr">
@@ -30471,7 +30471,7 @@
         <v>517</v>
       </c>
       <c r="N518" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519" ht="30" customHeight="1">
@@ -30494,7 +30494,7 @@
       </c>
       <c r="F519" s="1" t="inlineStr">
         <is>
-          <t>alphabetical order</t>
+          <t>glove</t>
         </is>
       </c>
       <c r="G519" s="1" t="inlineStr">
@@ -30529,7 +30529,7 @@
         <v>518</v>
       </c>
       <c r="N519" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="520" ht="30" customHeight="1">
@@ -30552,7 +30552,7 @@
       </c>
       <c r="F520" s="1" t="inlineStr">
         <is>
-          <t>play an important role</t>
+          <t>add</t>
         </is>
       </c>
       <c r="G520" s="1" t="inlineStr">
@@ -30587,7 +30587,7 @@
         <v>519</v>
       </c>
       <c r="N520" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521" ht="30" customHeight="1">
@@ -30610,7 +30610,7 @@
       </c>
       <c r="F521" s="1" t="inlineStr">
         <is>
-          <t>flight</t>
+          <t>envelope</t>
         </is>
       </c>
       <c r="G521" s="1" t="inlineStr">
@@ -30645,7 +30645,7 @@
         <v>520</v>
       </c>
       <c r="N521" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522" ht="30" customHeight="1">
@@ -30664,11 +30664,11 @@
         <v>2</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F522" s="1" t="inlineStr">
         <is>
-          <t>schedule</t>
+          <t>absolutely</t>
         </is>
       </c>
       <c r="G522" s="1" t="inlineStr">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="F523" s="1" t="inlineStr">
         <is>
-          <t>everywhere</t>
+          <t>seem</t>
         </is>
       </c>
       <c r="G523" s="1" t="inlineStr">
@@ -30761,7 +30761,7 @@
         <v>522</v>
       </c>
       <c r="N523" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="524" ht="30" customHeight="1">
@@ -30784,7 +30784,7 @@
       </c>
       <c r="F524" s="1" t="inlineStr">
         <is>
-          <t>challenge</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G524" s="1" t="inlineStr">
@@ -30819,7 +30819,7 @@
         <v>523</v>
       </c>
       <c r="N524" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="525" ht="30" customHeight="1">
@@ -30842,7 +30842,7 @@
       </c>
       <c r="F525" s="1" t="inlineStr">
         <is>
-          <t>prize</t>
+          <t>single</t>
         </is>
       </c>
       <c r="G525" s="1" t="inlineStr">
@@ -30877,7 +30877,7 @@
         <v>524</v>
       </c>
       <c r="N525" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526" ht="30" customHeight="1">
@@ -30900,7 +30900,7 @@
       </c>
       <c r="F526" s="1" t="inlineStr">
         <is>
-          <t>promise</t>
+          <t>nail</t>
         </is>
       </c>
       <c r="G526" s="1" t="inlineStr">
@@ -30935,7 +30935,7 @@
         <v>525</v>
       </c>
       <c r="N526" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527" ht="30" customHeight="1">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="F527" s="1" t="inlineStr">
         <is>
-          <t>chessboard</t>
+          <t>explain</t>
         </is>
       </c>
       <c r="G527" s="1" t="inlineStr">
@@ -30993,7 +30993,7 @@
         <v>526</v>
       </c>
       <c r="N527" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="528" ht="30" customHeight="1">
@@ -31016,7 +31016,7 @@
       </c>
       <c r="F528" s="1" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>bit</t>
         </is>
       </c>
       <c r="G528" s="1" t="inlineStr">
@@ -31051,7 +31051,7 @@
         <v>527</v>
       </c>
       <c r="N528" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529" ht="30" customHeight="1">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="F529" s="1" t="inlineStr">
         <is>
-          <t>reply</t>
+          <t>similar</t>
         </is>
       </c>
       <c r="G529" s="1" t="inlineStr">
@@ -31109,7 +31109,7 @@
         <v>528</v>
       </c>
       <c r="N529" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530" ht="30" customHeight="1">
@@ -31132,7 +31132,7 @@
       </c>
       <c r="F530" s="1" t="inlineStr">
         <is>
-          <t>hesitation</t>
+          <t>coin</t>
         </is>
       </c>
       <c r="G530" s="1" t="inlineStr">
@@ -31167,7 +31167,7 @@
         <v>529</v>
       </c>
       <c r="N530" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="531" ht="30" customHeight="1">
@@ -31190,7 +31190,7 @@
       </c>
       <c r="F531" s="1" t="inlineStr">
         <is>
-          <t>wonder</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="G531" s="1" t="inlineStr">
@@ -31225,7 +31225,7 @@
         <v>530</v>
       </c>
       <c r="N531" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532" ht="30" customHeight="1">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="F532" s="1" t="inlineStr">
         <is>
-          <t>agree</t>
+          <t>sticker</t>
         </is>
       </c>
       <c r="G532" s="1" t="inlineStr">
@@ -31283,7 +31283,7 @@
         <v>531</v>
       </c>
       <c r="N532" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="533" ht="30" customHeight="1">
@@ -31306,7 +31306,7 @@
       </c>
       <c r="F533" s="1" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>waste</t>
         </is>
       </c>
       <c r="G533" s="1" t="inlineStr">
@@ -31341,7 +31341,7 @@
         <v>532</v>
       </c>
       <c r="N533" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="534" ht="30" customHeight="1">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="F534" s="1" t="inlineStr">
         <is>
-          <t>currently</t>
+          <t>item</t>
         </is>
       </c>
       <c r="G534" s="1" t="inlineStr">
@@ -31399,7 +31399,7 @@
         <v>533</v>
       </c>
       <c r="N534" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535" ht="30" customHeight="1">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="F535" s="1" t="inlineStr">
         <is>
-          <t>check</t>
+          <t>result</t>
         </is>
       </c>
       <c r="G535" s="1" t="inlineStr">
@@ -31457,7 +31457,7 @@
         <v>534</v>
       </c>
       <c r="N535" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="536" ht="30" customHeight="1">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="F536" s="1" t="inlineStr">
         <is>
-          <t>budget</t>
+          <t>wrapper</t>
         </is>
       </c>
       <c r="G536" s="1" t="inlineStr">
@@ -31515,7 +31515,7 @@
         <v>535</v>
       </c>
       <c r="N536" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="537" ht="30" customHeight="1">
@@ -31538,7 +31538,7 @@
       </c>
       <c r="F537" s="1" t="inlineStr">
         <is>
-          <t>province</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="G537" s="1" t="inlineStr">
@@ -31573,7 +31573,7 @@
         <v>536</v>
       </c>
       <c r="N537" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538" ht="30" customHeight="1">
@@ -31596,7 +31596,7 @@
       </c>
       <c r="F538" s="1" t="inlineStr">
         <is>
-          <t>sharply</t>
+          <t>include</t>
         </is>
       </c>
       <c r="G538" s="1" t="inlineStr">
@@ -31631,7 +31631,7 @@
         <v>537</v>
       </c>
       <c r="N538" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="539" ht="30" customHeight="1">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="F539" s="1" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>size</t>
         </is>
       </c>
       <c r="G539" s="1" t="inlineStr">
@@ -31689,7 +31689,7 @@
         <v>538</v>
       </c>
       <c r="N539" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540" ht="30" customHeight="1">
@@ -31712,7 +31712,7 @@
       </c>
       <c r="F540" s="1" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="G540" s="1" t="inlineStr">
@@ -31747,7 +31747,7 @@
         <v>539</v>
       </c>
       <c r="N540" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541" ht="30" customHeight="1">
@@ -31770,7 +31770,7 @@
       </c>
       <c r="F541" s="1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>produce</t>
         </is>
       </c>
       <c r="G541" s="1" t="inlineStr">
@@ -31805,7 +31805,7 @@
         <v>540</v>
       </c>
       <c r="N541" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="542" ht="30" customHeight="1">
@@ -31828,7 +31828,7 @@
       </c>
       <c r="F542" s="1" t="inlineStr">
         <is>
-          <t>represent</t>
+          <t>attract</t>
         </is>
       </c>
       <c r="G542" s="1" t="inlineStr">
@@ -31863,7 +31863,7 @@
         <v>541</v>
       </c>
       <c r="N542" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543" ht="30" customHeight="1">
@@ -31886,7 +31886,7 @@
       </c>
       <c r="F543" s="1" t="inlineStr">
         <is>
-          <t>exactly</t>
+          <t>insect</t>
         </is>
       </c>
       <c r="G543" s="1" t="inlineStr">
@@ -31921,7 +31921,7 @@
         <v>542</v>
       </c>
       <c r="N543" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544" ht="30" customHeight="1">
@@ -31944,7 +31944,7 @@
       </c>
       <c r="F544" s="1" t="inlineStr">
         <is>
-          <t>flight schedule</t>
+          <t>object</t>
         </is>
       </c>
       <c r="G544" s="1" t="inlineStr">
@@ -31979,7 +31979,7 @@
         <v>543</v>
       </c>
       <c r="N544" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545" ht="30" customHeight="1">
@@ -32002,7 +32002,7 @@
       </c>
       <c r="F545" s="1" t="inlineStr">
         <is>
-          <t>price tag</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G545" s="1" t="inlineStr">
@@ -32037,7 +32037,7 @@
         <v>544</v>
       </c>
       <c r="N545" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546" ht="30" customHeight="1">
@@ -32060,7 +32060,7 @@
       </c>
       <c r="F546" s="1" t="inlineStr">
         <is>
-          <t>for a moment</t>
+          <t>language</t>
         </is>
       </c>
       <c r="G546" s="1" t="inlineStr">
@@ -32095,7 +32095,7 @@
         <v>545</v>
       </c>
       <c r="N546" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547" ht="30" customHeight="1">
@@ -32118,7 +32118,7 @@
       </c>
       <c r="F547" s="1" t="inlineStr">
         <is>
-          <t>without hesitation</t>
+          <t>treasure</t>
         </is>
       </c>
       <c r="G547" s="1" t="inlineStr">
@@ -32176,7 +32176,7 @@
       </c>
       <c r="F548" s="1" t="inlineStr">
         <is>
-          <t>go up</t>
+          <t>unlock</t>
         </is>
       </c>
       <c r="G548" s="1" t="inlineStr">
@@ -32211,7 +32211,7 @@
         <v>547</v>
       </c>
       <c r="N548" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549" ht="30" customHeight="1">
@@ -32234,7 +32234,7 @@
       </c>
       <c r="F549" s="1" t="inlineStr">
         <is>
-          <t>go down</t>
+          <t>real</t>
         </is>
       </c>
       <c r="G549" s="1" t="inlineStr">
@@ -32269,7 +32269,7 @@
         <v>548</v>
       </c>
       <c r="N549" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550" ht="30" customHeight="1">
@@ -32292,7 +32292,7 @@
       </c>
       <c r="F550" s="1" t="inlineStr">
         <is>
-          <t>write down</t>
+          <t>encourage</t>
         </is>
       </c>
       <c r="G550" s="1" t="inlineStr">
@@ -32327,7 +32327,7 @@
         <v>549</v>
       </c>
       <c r="N550" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551" ht="30" customHeight="1">
@@ -32350,7 +32350,7 @@
       </c>
       <c r="F551" s="1" t="inlineStr">
         <is>
-          <t>instead of</t>
+          <t>retire</t>
         </is>
       </c>
       <c r="G551" s="1" t="inlineStr">
@@ -32408,7 +32408,7 @@
       </c>
       <c r="F552" s="1" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>cheerful</t>
         </is>
       </c>
       <c r="G552" s="1" t="inlineStr">
@@ -32466,7 +32466,7 @@
       </c>
       <c r="F553" s="1" t="inlineStr">
         <is>
-          <t>flood</t>
+          <t>community</t>
         </is>
       </c>
       <c r="G553" s="1" t="inlineStr">
@@ -32501,7 +32501,7 @@
         <v>552</v>
       </c>
       <c r="N553" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554" ht="30" customHeight="1">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="F554" s="1" t="inlineStr">
         <is>
-          <t>multimedia</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="G554" s="1" t="inlineStr">
@@ -32559,7 +32559,7 @@
         <v>553</v>
       </c>
       <c r="N554" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555" ht="30" customHeight="1">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="F555" s="1" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>fried</t>
         </is>
       </c>
       <c r="G555" s="1" t="inlineStr">
@@ -32617,7 +32617,7 @@
         <v>554</v>
       </c>
       <c r="N555" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556" ht="30" customHeight="1">
@@ -32640,7 +32640,7 @@
       </c>
       <c r="F556" s="1" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>wherever</t>
         </is>
       </c>
       <c r="G556" s="1" t="inlineStr">
@@ -32675,7 +32675,7 @@
         <v>555</v>
       </c>
       <c r="N556" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="557" ht="30" customHeight="1">
@@ -32698,7 +32698,7 @@
       </c>
       <c r="F557" s="1" t="inlineStr">
         <is>
-          <t>payment</t>
+          <t>future</t>
         </is>
       </c>
       <c r="G557" s="1" t="inlineStr">
@@ -32733,7 +32733,7 @@
         <v>556</v>
       </c>
       <c r="N557" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="558" ht="30" customHeight="1">
@@ -32756,7 +32756,7 @@
       </c>
       <c r="F558" s="1" t="inlineStr">
         <is>
-          <t>warn</t>
+          <t>soon</t>
         </is>
       </c>
       <c r="G558" s="1" t="inlineStr">
@@ -32791,7 +32791,7 @@
         <v>557</v>
       </c>
       <c r="N558" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559" ht="30" customHeight="1">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="F559" s="1" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>smart</t>
         </is>
       </c>
       <c r="G559" s="1" t="inlineStr">
@@ -32849,7 +32849,7 @@
         <v>558</v>
       </c>
       <c r="N559" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560" ht="30" customHeight="1">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="F560" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>attention</t>
         </is>
       </c>
       <c r="G560" s="1" t="inlineStr">
@@ -32930,7 +32930,7 @@
       </c>
       <c r="F561" s="1" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>seldom</t>
         </is>
       </c>
       <c r="G561" s="1" t="inlineStr">
@@ -32965,7 +32965,7 @@
         <v>560</v>
       </c>
       <c r="N561" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="562" ht="30" customHeight="1">
@@ -32988,7 +32988,7 @@
       </c>
       <c r="F562" s="1" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>bored</t>
         </is>
       </c>
       <c r="G562" s="1" t="inlineStr">
@@ -33023,7 +33023,7 @@
         <v>561</v>
       </c>
       <c r="N562" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="563" ht="30" customHeight="1">
@@ -33046,7 +33046,7 @@
       </c>
       <c r="F563" s="1" t="inlineStr">
         <is>
-          <t>flow</t>
+          <t>strict</t>
         </is>
       </c>
       <c r="G563" s="1" t="inlineStr">
@@ -33104,7 +33104,7 @@
       </c>
       <c r="F564" s="1" t="inlineStr">
         <is>
-          <t>smoothly</t>
+          <t>relative</t>
         </is>
       </c>
       <c r="G564" s="1" t="inlineStr">
@@ -33162,7 +33162,7 @@
       </c>
       <c r="F565" s="1" t="inlineStr">
         <is>
-          <t>laptop</t>
+          <t>uniform</t>
         </is>
       </c>
       <c r="G565" s="1" t="inlineStr">
@@ -33220,7 +33220,7 @@
       </c>
       <c r="F566" s="1" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>personality</t>
         </is>
       </c>
       <c r="G566" s="1" t="inlineStr">
@@ -33278,7 +33278,7 @@
       </c>
       <c r="F567" s="1" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>characteristic</t>
         </is>
       </c>
       <c r="G567" s="1" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="F568" s="1" t="inlineStr">
         <is>
-          <t>digital</t>
+          <t>topic</t>
         </is>
       </c>
       <c r="G568" s="1" t="inlineStr">
@@ -33371,7 +33371,7 @@
         <v>567</v>
       </c>
       <c r="N568" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="569" ht="30" customHeight="1">
@@ -33394,7 +33394,7 @@
       </c>
       <c r="F569" s="1" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>café</t>
         </is>
       </c>
       <c r="G569" s="1" t="inlineStr">
@@ -33429,7 +33429,7 @@
         <v>568</v>
       </c>
       <c r="N569" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="570" ht="30" customHeight="1">
@@ -33452,7 +33452,7 @@
       </c>
       <c r="F570" s="1" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="G570" s="1" t="inlineStr">
@@ -33510,7 +33510,7 @@
       </c>
       <c r="F571" s="1" t="inlineStr">
         <is>
-          <t>interview</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="G571" s="1" t="inlineStr">
@@ -33568,7 +33568,7 @@
       </c>
       <c r="F572" s="1" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>perfect</t>
         </is>
       </c>
       <c r="G572" s="1" t="inlineStr">
@@ -33603,7 +33603,7 @@
         <v>571</v>
       </c>
       <c r="N572" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="573" ht="30" customHeight="1">
@@ -33626,7 +33626,7 @@
       </c>
       <c r="F573" s="1" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>mostly</t>
         </is>
       </c>
       <c r="G573" s="1" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="F574" s="1" t="inlineStr">
         <is>
-          <t>effect</t>
+          <t>receive</t>
         </is>
       </c>
       <c r="G574" s="1" t="inlineStr">
@@ -33742,7 +33742,7 @@
       </c>
       <c r="F575" s="1" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>key</t>
         </is>
       </c>
       <c r="G575" s="1" t="inlineStr">
@@ -33777,7 +33777,7 @@
         <v>574</v>
       </c>
       <c r="N575" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576" ht="30" customHeight="1">
@@ -33800,7 +33800,7 @@
       </c>
       <c r="F576" s="1" t="inlineStr">
         <is>
-          <t>novel</t>
+          <t>remain</t>
         </is>
       </c>
       <c r="G576" s="1" t="inlineStr">
@@ -33858,7 +33858,7 @@
       </c>
       <c r="F577" s="1" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>lift</t>
         </is>
       </c>
       <c r="G577" s="1" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="F578" s="1" t="inlineStr">
         <is>
-          <t>basis</t>
+          <t>step</t>
         </is>
       </c>
       <c r="G578" s="1" t="inlineStr">
@@ -33951,7 +33951,7 @@
         <v>577</v>
       </c>
       <c r="N578" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="579" ht="30" customHeight="1">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="F579" s="1" t="inlineStr">
         <is>
-          <t>microprocessor</t>
+          <t>stair</t>
         </is>
       </c>
       <c r="G579" s="1" t="inlineStr">
@@ -34009,7 +34009,7 @@
         <v>578</v>
       </c>
       <c r="N579" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="580" ht="30" customHeight="1">
@@ -34032,7 +34032,7 @@
       </c>
       <c r="F580" s="1" t="inlineStr">
         <is>
-          <t>microchip</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="G580" s="1" t="inlineStr">
@@ -34090,7 +34090,7 @@
       </c>
       <c r="F581" s="1" t="inlineStr">
         <is>
-          <t>major</t>
+          <t>sightseeing</t>
         </is>
       </c>
       <c r="G581" s="1" t="inlineStr">
@@ -34148,7 +34148,7 @@
       </c>
       <c r="F582" s="1" t="inlineStr">
         <is>
-          <t>breakthrough</t>
+          <t>imagine</t>
         </is>
       </c>
       <c r="G582" s="1" t="inlineStr">
@@ -34183,7 +34183,7 @@
         <v>581</v>
       </c>
       <c r="N582" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="583" ht="30" customHeight="1">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="F583" s="1" t="inlineStr">
         <is>
-          <t>electronic</t>
+          <t>destination</t>
         </is>
       </c>
       <c r="G583" s="1" t="inlineStr">
@@ -34241,7 +34241,7 @@
         <v>582</v>
       </c>
       <c r="N583" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="584" ht="30" customHeight="1">
@@ -34264,7 +34264,7 @@
       </c>
       <c r="F584" s="1" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>address</t>
         </is>
       </c>
       <c r="G584" s="1" t="inlineStr">
@@ -34299,7 +34299,7 @@
         <v>583</v>
       </c>
       <c r="N584" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585" ht="30" customHeight="1">
@@ -34322,7 +34322,7 @@
       </c>
       <c r="F585" s="1" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>government</t>
         </is>
       </c>
       <c r="G585" s="1" t="inlineStr">
@@ -34357,7 +34357,7 @@
         <v>584</v>
       </c>
       <c r="N585" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="586" ht="30" customHeight="1">
@@ -34380,7 +34380,7 @@
       </c>
       <c r="F586" s="1" t="inlineStr">
         <is>
-          <t>era</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="G586" s="1" t="inlineStr">
@@ -34438,7 +34438,7 @@
       </c>
       <c r="F587" s="1" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>endangered</t>
         </is>
       </c>
       <c r="G587" s="1" t="inlineStr">
@@ -34496,7 +34496,7 @@
       </c>
       <c r="F588" s="1" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>stretch</t>
         </is>
       </c>
       <c r="G588" s="1" t="inlineStr">
@@ -34554,7 +34554,7 @@
       </c>
       <c r="F589" s="1" t="inlineStr">
         <is>
-          <t>connect to</t>
+          <t>huge</t>
         </is>
       </c>
       <c r="G589" s="1" t="inlineStr">
@@ -34589,7 +34589,7 @@
         <v>588</v>
       </c>
       <c r="N589" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="590" ht="30" customHeight="1">
@@ -34612,7 +34612,7 @@
       </c>
       <c r="F590" s="1" t="inlineStr">
         <is>
-          <t>bring big changes to</t>
+          <t>wild</t>
         </is>
       </c>
       <c r="G590" s="1" t="inlineStr">
@@ -34647,7 +34647,7 @@
         <v>589</v>
       </c>
       <c r="N590" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="591" ht="30" customHeight="1">
@@ -34670,7 +34670,7 @@
       </c>
       <c r="F591" s="1" t="inlineStr">
         <is>
-          <t>mobile payment</t>
+          <t>discover</t>
         </is>
       </c>
       <c r="G591" s="1" t="inlineStr">
@@ -34728,7 +34728,7 @@
       </c>
       <c r="F592" s="1" t="inlineStr">
         <is>
-          <t>take...for example</t>
+          <t>volcano</t>
         </is>
       </c>
       <c r="G592" s="1" t="inlineStr">
@@ -34763,7 +34763,7 @@
         <v>591</v>
       </c>
       <c r="N592" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="593" ht="30" customHeight="1">
@@ -34786,7 +34786,7 @@
       </c>
       <c r="F593" s="1" t="inlineStr">
         <is>
-          <t>rubbish bin</t>
+          <t>range</t>
         </is>
       </c>
       <c r="G593" s="1" t="inlineStr">
@@ -34844,7 +34844,7 @@
       </c>
       <c r="F594" s="1" t="inlineStr">
         <is>
-          <t>social media</t>
+          <t>snowmobile</t>
         </is>
       </c>
       <c r="G594" s="1" t="inlineStr">
@@ -34902,7 +34902,7 @@
       </c>
       <c r="F595" s="1" t="inlineStr">
         <is>
-          <t>in person</t>
+          <t>wolf</t>
         </is>
       </c>
       <c r="G595" s="1" t="inlineStr">
@@ -34937,7 +34937,7 @@
         <v>594</v>
       </c>
       <c r="N595" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="596" ht="30" customHeight="1">
@@ -34960,7 +34960,7 @@
       </c>
       <c r="F596" s="1" t="inlineStr">
         <is>
-          <t>the general public</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="G596" s="1" t="inlineStr">
@@ -34995,7 +34995,7 @@
         <v>595</v>
       </c>
       <c r="N596" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="597" ht="30" customHeight="1">
@@ -35018,7 +35018,7 @@
       </c>
       <c r="F597" s="1" t="inlineStr">
         <is>
-          <t>balloon</t>
+          <t>root</t>
         </is>
       </c>
       <c r="G597" s="1" t="inlineStr">
@@ -35076,7 +35076,7 @@
       </c>
       <c r="F598" s="1" t="inlineStr">
         <is>
-          <t>wheel</t>
+          <t>silent</t>
         </is>
       </c>
       <c r="G598" s="1" t="inlineStr">
@@ -35111,7 +35111,7 @@
         <v>597</v>
       </c>
       <c r="N598" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="599" ht="30" customHeight="1">
@@ -35134,7 +35134,7 @@
       </c>
       <c r="F599" s="1" t="inlineStr">
         <is>
-          <t>central</t>
+          <t>overlook</t>
         </is>
       </c>
       <c r="G599" s="1" t="inlineStr">
@@ -35192,7 +35192,7 @@
       </c>
       <c r="F600" s="1" t="inlineStr">
         <is>
-          <t>although</t>
+          <t>human</t>
         </is>
       </c>
       <c r="G600" s="1" t="inlineStr">
@@ -35227,7 +35227,7 @@
         <v>599</v>
       </c>
       <c r="N600" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="601" ht="30" customHeight="1">
@@ -35250,7 +35250,7 @@
       </c>
       <c r="F601" s="1" t="inlineStr">
         <is>
-          <t>attach</t>
+          <t>oxygen</t>
         </is>
       </c>
       <c r="G601" s="1" t="inlineStr">
@@ -35308,7 +35308,7 @@
       </c>
       <c r="F602" s="1" t="inlineStr">
         <is>
-          <t>pull</t>
+          <t>create</t>
         </is>
       </c>
       <c r="G602" s="1" t="inlineStr">
@@ -35343,7 +35343,7 @@
         <v>601</v>
       </c>
       <c r="N602" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="603" ht="30" customHeight="1">
@@ -35366,7 +35366,7 @@
       </c>
       <c r="F603" s="1" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>environment</t>
         </is>
       </c>
       <c r="G603" s="1" t="inlineStr">
@@ -35424,7 +35424,7 @@
       </c>
       <c r="F604" s="1" t="inlineStr">
         <is>
-          <t>path</t>
+          <t>convenient</t>
         </is>
       </c>
       <c r="G604" s="1" t="inlineStr">
@@ -35459,7 +35459,7 @@
         <v>603</v>
       </c>
       <c r="N604" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="605" ht="30" customHeight="1">
@@ -35482,7 +35482,7 @@
       </c>
       <c r="F605" s="1" t="inlineStr">
         <is>
-          <t>technique</t>
+          <t>furniture</t>
         </is>
       </c>
       <c r="G605" s="1" t="inlineStr">
@@ -35540,7 +35540,7 @@
       </c>
       <c r="F606" s="1" t="inlineStr">
         <is>
-          <t>depend</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="G606" s="1" t="inlineStr">
@@ -35575,7 +35575,7 @@
         <v>605</v>
       </c>
       <c r="N606" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="607" ht="30" customHeight="1">
@@ -35598,7 +35598,7 @@
       </c>
       <c r="F607" s="1" t="inlineStr">
         <is>
-          <t>doubt</t>
+          <t>treat</t>
         </is>
       </c>
       <c r="G607" s="1" t="inlineStr">
@@ -35656,7 +35656,7 @@
       </c>
       <c r="F608" s="1" t="inlineStr">
         <is>
-          <t>personally</t>
+          <t>communicate</t>
         </is>
       </c>
       <c r="G608" s="1" t="inlineStr">
@@ -35714,7 +35714,7 @@
       </c>
       <c r="F609" s="1" t="inlineStr">
         <is>
-          <t>prediction</t>
+          <t>species</t>
         </is>
       </c>
       <c r="G609" s="1" t="inlineStr">
@@ -35772,7 +35772,7 @@
       </c>
       <c r="F610" s="1" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>product</t>
         </is>
       </c>
       <c r="G610" s="1" t="inlineStr">
@@ -35830,7 +35830,7 @@
       </c>
       <c r="F611" s="1" t="inlineStr">
         <is>
-          <t>benefit</t>
+          <t>side</t>
         </is>
       </c>
       <c r="G611" s="1" t="inlineStr">
@@ -35865,7 +35865,7 @@
         <v>610</v>
       </c>
       <c r="N611" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="612" ht="30" customHeight="1">
@@ -35888,7 +35888,7 @@
       </c>
       <c r="F612" s="1" t="inlineStr">
         <is>
-          <t>wing</t>
+          <t>borrow</t>
         </is>
       </c>
       <c r="G612" s="1" t="inlineStr">
@@ -35923,7 +35923,7 @@
         <v>611</v>
       </c>
       <c r="N612" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="613" ht="30" customHeight="1">
@@ -35946,7 +35946,7 @@
       </c>
       <c r="F613" s="1" t="inlineStr">
         <is>
-          <t>distance</t>
+          <t>dig</t>
         </is>
       </c>
       <c r="G613" s="1" t="inlineStr">
@@ -35981,7 +35981,7 @@
         <v>612</v>
       </c>
       <c r="N613" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="614" ht="30" customHeight="1">
@@ -36004,7 +36004,7 @@
       </c>
       <c r="F614" s="1" t="inlineStr">
         <is>
-          <t>petrol</t>
+          <t>hole</t>
         </is>
       </c>
       <c r="G614" s="1" t="inlineStr">
@@ -36039,7 +36039,7 @@
         <v>613</v>
       </c>
       <c r="N614" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="615" ht="30" customHeight="1">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="F615" s="1" t="inlineStr">
         <is>
-          <t>avoid</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="G615" s="1" t="inlineStr">
@@ -36120,7 +36120,7 @@
       </c>
       <c r="F616" s="1" t="inlineStr">
         <is>
-          <t>anywhere</t>
+          <t>accident</t>
         </is>
       </c>
       <c r="G616" s="1" t="inlineStr">
@@ -36155,7 +36155,7 @@
         <v>615</v>
       </c>
       <c r="N616" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="617" ht="30" customHeight="1">
@@ -36178,7 +36178,7 @@
       </c>
       <c r="F617" s="1" t="inlineStr">
         <is>
-          <t>notice</t>
+          <t>knowledge</t>
         </is>
       </c>
       <c r="G617" s="1" t="inlineStr">
@@ -36213,7 +36213,7 @@
         <v>616</v>
       </c>
       <c r="N617" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="618" ht="30" customHeight="1">
@@ -36236,7 +36236,7 @@
       </c>
       <c r="F618" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>character</t>
         </is>
       </c>
       <c r="G618" s="1" t="inlineStr">
@@ -36294,7 +36294,7 @@
       </c>
       <c r="F619" s="1" t="inlineStr">
         <is>
-          <t>mixture</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="G619" s="1" t="inlineStr">
@@ -36329,7 +36329,7 @@
         <v>618</v>
       </c>
       <c r="N619" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="620" ht="30" customHeight="1">
@@ -36352,7 +36352,7 @@
       </c>
       <c r="F620" s="1" t="inlineStr">
         <is>
-          <t>heat</t>
+          <t>translation</t>
         </is>
       </c>
       <c r="G620" s="1" t="inlineStr">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="F621" s="1" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>dolphin</t>
         </is>
       </c>
       <c r="G621" s="1" t="inlineStr">
@@ -36445,7 +36445,7 @@
         <v>620</v>
       </c>
       <c r="N621" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="622" ht="30" customHeight="1">
@@ -36468,7 +36468,7 @@
       </c>
       <c r="F622" s="1" t="inlineStr">
         <is>
-          <t>metal</t>
+          <t>hen</t>
         </is>
       </c>
       <c r="G622" s="1" t="inlineStr">
@@ -36503,7 +36503,7 @@
         <v>621</v>
       </c>
       <c r="N622" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="623" ht="30" customHeight="1">
@@ -36526,7 +36526,7 @@
       </c>
       <c r="F623" s="1" t="inlineStr">
         <is>
-          <t>steam locomotive</t>
+          <t>blind</t>
         </is>
       </c>
       <c r="G623" s="1" t="inlineStr">
@@ -36561,7 +36561,7 @@
         <v>622</v>
       </c>
       <c r="N623" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="624" ht="30" customHeight="1">
@@ -36584,7 +36584,7 @@
       </c>
       <c r="F624" s="1" t="inlineStr">
         <is>
-          <t>crewed spacecraft</t>
+          <t>wool</t>
         </is>
       </c>
       <c r="G624" s="1" t="inlineStr">
@@ -36619,7 +36619,7 @@
         <v>623</v>
       </c>
       <c r="N624" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="625" ht="30" customHeight="1">
@@ -36642,7 +36642,7 @@
       </c>
       <c r="F625" s="1" t="inlineStr">
         <is>
-          <t>on foot</t>
+          <t>sir</t>
         </is>
       </c>
       <c r="G625" s="1" t="inlineStr">
@@ -36677,7 +36677,7 @@
         <v>624</v>
       </c>
       <c r="N625" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="626" ht="30" customHeight="1">
@@ -36700,7 +36700,7 @@
       </c>
       <c r="F626" s="1" t="inlineStr">
         <is>
-          <t>a number of</t>
+          <t>receptionist</t>
         </is>
       </c>
       <c r="G626" s="1" t="inlineStr">
@@ -36758,7 +36758,7 @@
       </c>
       <c r="F627" s="1" t="inlineStr">
         <is>
-          <t>take place</t>
+          <t>allow</t>
         </is>
       </c>
       <c r="G627" s="1" t="inlineStr">
@@ -36816,7 +36816,7 @@
       </c>
       <c r="F628" s="1" t="inlineStr">
         <is>
-          <t>for instance</t>
+          <t>apologize</t>
         </is>
       </c>
       <c r="G628" s="1" t="inlineStr">
@@ -36874,7 +36874,7 @@
       </c>
       <c r="F629" s="1" t="inlineStr">
         <is>
-          <t>large amounts of</t>
+          <t>asleep</t>
         </is>
       </c>
       <c r="G629" s="1" t="inlineStr">
@@ -36909,7 +36909,7 @@
         <v>628</v>
       </c>
       <c r="N629" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="630" ht="30" customHeight="1">
@@ -36932,7 +36932,7 @@
       </c>
       <c r="F630" s="1" t="inlineStr">
         <is>
-          <t>international trade</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="G630" s="1" t="inlineStr">
@@ -36967,7 +36967,7 @@
         <v>629</v>
       </c>
       <c r="N630" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="631" ht="30" customHeight="1">
@@ -36990,7 +36990,7 @@
       </c>
       <c r="F631" s="1" t="inlineStr">
         <is>
-          <t>depend on</t>
+          <t>fireman</t>
         </is>
       </c>
       <c r="G631" s="1" t="inlineStr">
@@ -37025,7 +37025,7 @@
         <v>630</v>
       </c>
       <c r="N631" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="632" ht="30" customHeight="1">
@@ -37048,7 +37048,7 @@
       </c>
       <c r="F632" s="1" t="inlineStr">
         <is>
-          <t>3D printer</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G632" s="1" t="inlineStr">
@@ -37083,7 +37083,7 @@
         <v>631</v>
       </c>
       <c r="N632" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="633" ht="30" customHeight="1">
@@ -37106,7 +37106,7 @@
       </c>
       <c r="F633" s="1" t="inlineStr">
         <is>
-          <t>without doubt</t>
+          <t>search-and-rescue</t>
         </is>
       </c>
       <c r="G633" s="1" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="F634" s="1" t="inlineStr">
         <is>
-          <t>of all time</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G634" s="1" t="inlineStr">
@@ -37222,7 +37222,7 @@
       </c>
       <c r="F635" s="1" t="inlineStr">
         <is>
-          <t>make fun of</t>
+          <t>disaster</t>
         </is>
       </c>
       <c r="G635" s="1" t="inlineStr">
@@ -37280,7 +37280,7 @@
       </c>
       <c r="F636" s="1" t="inlineStr">
         <is>
-          <t>traffic jam</t>
+          <t>guest</t>
         </is>
       </c>
       <c r="G636" s="1" t="inlineStr">
@@ -37338,7 +37338,7 @@
       </c>
       <c r="F637" s="1" t="inlineStr">
         <is>
-          <t>exchange</t>
+          <t>team</t>
         </is>
       </c>
       <c r="G637" s="1" t="inlineStr">
@@ -37373,7 +37373,7 @@
         <v>636</v>
       </c>
       <c r="N637" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="638" ht="30" customHeight="1">
@@ -37396,7 +37396,7 @@
       </c>
       <c r="F638" s="1" t="inlineStr">
         <is>
-          <t>nervous</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="G638" s="1" t="inlineStr">
@@ -37431,7 +37431,7 @@
         <v>637</v>
       </c>
       <c r="N638" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="639" ht="30" customHeight="1">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="F639" s="1" t="inlineStr">
         <is>
-          <t>grateful</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="G639" s="1" t="inlineStr">
@@ -37512,7 +37512,7 @@
       </c>
       <c r="F640" s="1" t="inlineStr">
         <is>
-          <t>chopstick</t>
+          <t>honey</t>
         </is>
       </c>
       <c r="G640" s="1" t="inlineStr">
@@ -37543,7 +37543,7 @@
         <v>639</v>
       </c>
       <c r="N640" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="641" ht="30" customHeight="1">
@@ -37566,7 +37566,7 @@
       </c>
       <c r="F641" s="1" t="inlineStr">
         <is>
-          <t>tour</t>
+          <t>material</t>
         </is>
       </c>
       <c r="G641" s="1" t="inlineStr">
@@ -37624,7 +37624,7 @@
       </c>
       <c r="F642" s="1" t="inlineStr">
         <is>
-          <t>tai chi</t>
+          <t>either</t>
         </is>
       </c>
       <c r="G642" s="1" t="inlineStr">
@@ -37655,7 +37655,7 @@
         <v>641</v>
       </c>
       <c r="N642" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="643" ht="30" customHeight="1">
@@ -37678,7 +37678,7 @@
       </c>
       <c r="F643" s="1" t="inlineStr">
         <is>
-          <t>yet</t>
+          <t>shark</t>
         </is>
       </c>
       <c r="G643" s="1" t="inlineStr">
@@ -37713,7 +37713,7 @@
         <v>642</v>
       </c>
       <c r="N643" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="644" ht="30" customHeight="1">
@@ -37736,7 +37736,7 @@
       </c>
       <c r="F644" s="1" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>scared</t>
         </is>
       </c>
       <c r="G644" s="1" t="inlineStr">
@@ -37771,7 +37771,7 @@
         <v>643</v>
       </c>
       <c r="N644" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="645" ht="30" customHeight="1">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="F645" s="1" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>grey</t>
         </is>
       </c>
       <c r="G645" s="1" t="inlineStr">
@@ -37829,7 +37829,7 @@
         <v>644</v>
       </c>
       <c r="N645" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="646" ht="30" customHeight="1">
@@ -37852,7 +37852,7 @@
       </c>
       <c r="F646" s="1" t="inlineStr">
         <is>
-          <t>feeling</t>
+          <t>somewhere</t>
         </is>
       </c>
       <c r="G646" s="1" t="inlineStr">
@@ -37910,7 +37910,7 @@
       </c>
       <c r="F647" s="1" t="inlineStr">
         <is>
-          <t>shock</t>
+          <t>probably</t>
         </is>
       </c>
       <c r="G647" s="1" t="inlineStr">
@@ -37968,7 +37968,7 @@
       </c>
       <c r="F648" s="1" t="inlineStr">
         <is>
-          <t>foreign</t>
+          <t>source</t>
         </is>
       </c>
       <c r="G648" s="1" t="inlineStr">
@@ -38026,7 +38026,7 @@
       </c>
       <c r="F649" s="1" t="inlineStr">
         <is>
-          <t>confused</t>
+          <t>sometime</t>
         </is>
       </c>
       <c r="G649" s="1" t="inlineStr">
@@ -38084,7 +38084,7 @@
       </c>
       <c r="F650" s="1" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>extinct</t>
         </is>
       </c>
       <c r="G650" s="1" t="inlineStr">
@@ -38142,7 +38142,7 @@
       </c>
       <c r="F651" s="1" t="inlineStr">
         <is>
-          <t>phase</t>
+          <t>effort</t>
         </is>
       </c>
       <c r="G651" s="1" t="inlineStr">
@@ -38200,7 +38200,7 @@
       </c>
       <c r="F652" s="1" t="inlineStr">
         <is>
-          <t>honeymoon</t>
+          <t>everyday</t>
         </is>
       </c>
       <c r="G652" s="1" t="inlineStr">
@@ -38231,7 +38231,7 @@
         <v>651</v>
       </c>
       <c r="N652" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="653" ht="30" customHeight="1">
@@ -38254,7 +38254,7 @@
       </c>
       <c r="F653" s="1" t="inlineStr">
         <is>
-          <t>unfamiliar</t>
+          <t>form</t>
         </is>
       </c>
       <c r="G653" s="1" t="inlineStr">
@@ -38289,7 +38289,7 @@
         <v>652</v>
       </c>
       <c r="N653" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="654" ht="30" customHeight="1">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="F654" s="1" t="inlineStr">
         <is>
-          <t>homesick</t>
+          <t>journey</t>
         </is>
       </c>
       <c r="G654" s="1" t="inlineStr">
@@ -38343,7 +38343,7 @@
         <v>653</v>
       </c>
       <c r="N654" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="655" ht="30" customHeight="1">
@@ -38366,7 +38366,7 @@
       </c>
       <c r="F655" s="1" t="inlineStr">
         <is>
-          <t>lonely</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="G655" s="1" t="inlineStr">
@@ -38401,7 +38401,7 @@
         <v>654</v>
       </c>
       <c r="N655" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="656" ht="30" customHeight="1">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="F656" s="1" t="inlineStr">
         <is>
-          <t>deal</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="G656" s="1" t="inlineStr">
@@ -38459,7 +38459,7 @@
         <v>655</v>
       </c>
       <c r="N656" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="657" ht="30" customHeight="1">
@@ -38482,7 +38482,7 @@
       </c>
       <c r="F657" s="1" t="inlineStr">
         <is>
-          <t>expect</t>
+          <t>voice</t>
         </is>
       </c>
       <c r="G657" s="1" t="inlineStr">
@@ -38517,7 +38517,7 @@
         <v>656</v>
       </c>
       <c r="N657" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="658" ht="30" customHeight="1">
@@ -38540,7 +38540,7 @@
       </c>
       <c r="F658" s="1" t="inlineStr">
         <is>
-          <t>situation</t>
+          <t>eventually</t>
         </is>
       </c>
       <c r="G658" s="1" t="inlineStr">
@@ -38598,7 +38598,7 @@
       </c>
       <c r="F659" s="1" t="inlineStr">
         <is>
-          <t>accept</t>
+          <t>pipe</t>
         </is>
       </c>
       <c r="G659" s="1" t="inlineStr">
@@ -38656,7 +38656,7 @@
       </c>
       <c r="F660" s="1" t="inlineStr">
         <is>
-          <t>adaptation</t>
+          <t>return</t>
         </is>
       </c>
       <c r="G660" s="1" t="inlineStr">
@@ -38691,7 +38691,7 @@
         <v>659</v>
       </c>
       <c r="N660" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="661" ht="30" customHeight="1">
@@ -38714,7 +38714,7 @@
       </c>
       <c r="F661" s="1" t="inlineStr">
         <is>
-          <t>beijing opera</t>
+          <t>rush</t>
         </is>
       </c>
       <c r="G661" s="1" t="inlineStr">
@@ -38745,7 +38745,7 @@
         <v>660</v>
       </c>
       <c r="N661" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="662" ht="30" customHeight="1">
@@ -38768,7 +38768,7 @@
       </c>
       <c r="F662" s="1" t="inlineStr">
         <is>
-          <t>host family</t>
+          <t>bath</t>
         </is>
       </c>
       <c r="G662" s="1" t="inlineStr">
@@ -38799,7 +38799,7 @@
         <v>661</v>
       </c>
       <c r="N662" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="663" ht="30" customHeight="1">
@@ -38822,7 +38822,7 @@
       </c>
       <c r="F663" s="1" t="inlineStr">
         <is>
-          <t>snake its way</t>
+          <t>salt</t>
         </is>
       </c>
       <c r="G663" s="1" t="inlineStr">
@@ -38857,7 +38857,7 @@
         <v>662</v>
       </c>
       <c r="N663" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="664" ht="30" customHeight="1">
@@ -38880,7 +38880,7 @@
       </c>
       <c r="F664" s="1" t="inlineStr">
         <is>
-          <t>culture shock</t>
+          <t>brain</t>
         </is>
       </c>
       <c r="G664" s="1" t="inlineStr">
@@ -38911,7 +38911,7 @@
         <v>663</v>
       </c>
       <c r="N664" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="665" ht="30" customHeight="1">
@@ -38934,7 +38934,7 @@
       </c>
       <c r="F665" s="1" t="inlineStr">
         <is>
-          <t>deal with</t>
+          <t>fix</t>
         </is>
       </c>
       <c r="G665" s="1" t="inlineStr">
@@ -38969,7 +38969,7 @@
         <v>664</v>
       </c>
       <c r="N665" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="666" ht="30" customHeight="1">
@@ -38992,7 +38992,7 @@
       </c>
       <c r="F666" s="1" t="inlineStr">
         <is>
-          <t>feel at home</t>
+          <t>public</t>
         </is>
       </c>
       <c r="G666" s="1" t="inlineStr">
@@ -39050,7 +39050,7 @@
       </c>
       <c r="F667" s="1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>population</t>
         </is>
       </c>
       <c r="G667" s="1" t="inlineStr">
@@ -39108,7 +39108,7 @@
       </c>
       <c r="F668" s="1" t="inlineStr">
         <is>
-          <t>remains</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="G668" s="1" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="F669" s="1" t="inlineStr">
         <is>
-          <t>locate</t>
+          <t>trade</t>
         </is>
       </c>
       <c r="G669" s="1" t="inlineStr">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="F670" s="1" t="inlineStr">
         <is>
-          <t>soldier</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="G670" s="1" t="inlineStr">
@@ -39282,7 +39282,7 @@
       </c>
       <c r="F671" s="1" t="inlineStr">
         <is>
-          <t>captain</t>
+          <t>role</t>
         </is>
       </c>
       <c r="G671" s="1" t="inlineStr">
@@ -39317,7 +39317,7 @@
         <v>670</v>
       </c>
       <c r="N671" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="672" ht="30" customHeight="1">
@@ -39340,7 +39340,7 @@
       </c>
       <c r="F672" s="1" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="G672" s="1" t="inlineStr">
@@ -39375,7 +39375,7 @@
         <v>671</v>
       </c>
       <c r="N672" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="673" ht="30" customHeight="1">
@@ -39398,7 +39398,7 @@
       </c>
       <c r="F673" s="1" t="inlineStr">
         <is>
-          <t>victory</t>
+          <t>overseas</t>
         </is>
       </c>
       <c r="G673" s="1" t="inlineStr">
@@ -39433,7 +39433,7 @@
         <v>672</v>
       </c>
       <c r="N673" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="674" ht="30" customHeight="1">
@@ -39456,7 +39456,7 @@
       </c>
       <c r="F674" s="1" t="inlineStr">
         <is>
-          <t>joke</t>
+          <t>global</t>
         </is>
       </c>
       <c r="G674" s="1" t="inlineStr">
@@ -39514,7 +39514,7 @@
       </c>
       <c r="F675" s="1" t="inlineStr">
         <is>
-          <t>midnight</t>
+          <t>income</t>
         </is>
       </c>
       <c r="G675" s="1" t="inlineStr">
@@ -39572,7 +39572,7 @@
       </c>
       <c r="F676" s="1" t="inlineStr">
         <is>
-          <t>except</t>
+          <t>nearly</t>
         </is>
       </c>
       <c r="G676" s="1" t="inlineStr">
@@ -39630,7 +39630,7 @@
       </c>
       <c r="F677" s="1" t="inlineStr">
         <is>
-          <t>hide</t>
+          <t>business</t>
         </is>
       </c>
       <c r="G677" s="1" t="inlineStr">
@@ -39665,7 +39665,7 @@
         <v>676</v>
       </c>
       <c r="N677" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="678" ht="30" customHeight="1">
@@ -39688,7 +39688,7 @@
       </c>
       <c r="F678" s="1" t="inlineStr">
         <is>
-          <t>secretly</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="G678" s="1" t="inlineStr">
@@ -39746,7 +39746,7 @@
       </c>
       <c r="F679" s="1" t="inlineStr">
         <is>
-          <t>enter</t>
+          <t>throughout</t>
         </is>
       </c>
       <c r="G679" s="1" t="inlineStr">
@@ -39804,7 +39804,7 @@
       </c>
       <c r="F680" s="1" t="inlineStr">
         <is>
-          <t>succeed</t>
+          <t>duty</t>
         </is>
       </c>
       <c r="G680" s="1" t="inlineStr">
@@ -39839,7 +39839,7 @@
         <v>679</v>
       </c>
       <c r="N680" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="681" ht="30" customHeight="1">
@@ -39862,7 +39862,7 @@
       </c>
       <c r="F681" s="1" t="inlineStr">
         <is>
-          <t>trick</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="G681" s="1" t="inlineStr">
@@ -39920,7 +39920,7 @@
       </c>
       <c r="F682" s="1" t="inlineStr">
         <is>
-          <t>fight</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="G682" s="1" t="inlineStr">
@@ -39955,7 +39955,7 @@
         <v>681</v>
       </c>
       <c r="N682" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="683" ht="30" customHeight="1">
@@ -39978,7 +39978,7 @@
       </c>
       <c r="F683" s="1" t="inlineStr">
         <is>
-          <t>beat</t>
+          <t>switch-off</t>
         </is>
       </c>
       <c r="G683" s="1" t="inlineStr">
@@ -40013,7 +40013,7 @@
         <v>682</v>
       </c>
       <c r="N683" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="684" ht="30" customHeight="1">
@@ -40036,7 +40036,7 @@
       </c>
       <c r="F684" s="1" t="inlineStr">
         <is>
-          <t>pretend</t>
+          <t>task</t>
         </is>
       </c>
       <c r="G684" s="1" t="inlineStr">
@@ -40071,7 +40071,7 @@
         <v>683</v>
       </c>
       <c r="N684" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="685" ht="30" customHeight="1">
@@ -40094,7 +40094,7 @@
       </c>
       <c r="F685" s="1" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>while</t>
         </is>
       </c>
       <c r="G685" s="1" t="inlineStr">
@@ -40152,7 +40152,7 @@
       </c>
       <c r="F686" s="1" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="G686" s="1" t="inlineStr">
@@ -40187,7 +40187,7 @@
         <v>685</v>
       </c>
       <c r="N686" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="687" ht="30" customHeight="1">
@@ -40210,7 +40210,7 @@
       </c>
       <c r="F687" s="1" t="inlineStr">
         <is>
-          <t>therefore</t>
+          <t>fridge</t>
         </is>
       </c>
       <c r="G687" s="1" t="inlineStr">
@@ -40245,7 +40245,7 @@
         <v>686</v>
       </c>
       <c r="N687" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="688" ht="30" customHeight="1">
@@ -40268,7 +40268,7 @@
       </c>
       <c r="F688" s="1" t="inlineStr">
         <is>
-          <t>within</t>
+          <t>yogurt</t>
         </is>
       </c>
       <c r="G688" s="1" t="inlineStr">
@@ -40326,7 +40326,7 @@
       </c>
       <c r="F689" s="1" t="inlineStr">
         <is>
-          <t>fill</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="G689" s="1" t="inlineStr">
@@ -40384,7 +40384,7 @@
       </c>
       <c r="F690" s="1" t="inlineStr">
         <is>
-          <t>towards</t>
+          <t>household</t>
         </is>
       </c>
       <c r="G690" s="1" t="inlineStr">
@@ -40442,7 +40442,7 @@
       </c>
       <c r="F691" s="1" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>against</t>
         </is>
       </c>
       <c r="G691" s="1" t="inlineStr">
@@ -40500,7 +40500,7 @@
       </c>
       <c r="F692" s="1" t="inlineStr">
         <is>
-          <t>fog</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="G692" s="1" t="inlineStr">
@@ -40558,7 +40558,7 @@
       </c>
       <c r="F693" s="1" t="inlineStr">
         <is>
-          <t>make jokes about</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="G693" s="1" t="inlineStr">
@@ -40593,7 +40593,7 @@
         <v>692</v>
       </c>
       <c r="N693" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="694" ht="30" customHeight="1">
@@ -40616,7 +40616,7 @@
       </c>
       <c r="F694" s="1" t="inlineStr">
         <is>
-          <t>succeed in</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="G694" s="1" t="inlineStr">
@@ -40674,7 +40674,7 @@
       </c>
       <c r="F695" s="1" t="inlineStr">
         <is>
-          <t>be tired of</t>
+          <t>connect</t>
         </is>
       </c>
       <c r="G695" s="1" t="inlineStr">
@@ -40709,7 +40709,7 @@
         <v>694</v>
       </c>
       <c r="N695" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="696" ht="30" customHeight="1">
@@ -40732,7 +40732,7 @@
       </c>
       <c r="F696" s="1" t="inlineStr">
         <is>
-          <t>go on board</t>
+          <t>device</t>
         </is>
       </c>
       <c r="G696" s="1" t="inlineStr">
@@ -40790,7 +40790,7 @@
       </c>
       <c r="F697" s="1" t="inlineStr">
         <is>
-          <t>be jealous of</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="G697" s="1" t="inlineStr">
@@ -40825,7 +40825,7 @@
         <v>696</v>
       </c>
       <c r="N697" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="698" ht="30" customHeight="1">
@@ -40848,7 +40848,7 @@
       </c>
       <c r="F698" s="1" t="inlineStr">
         <is>
-          <t>be full of</t>
+          <t>climate</t>
         </is>
       </c>
       <c r="G698" s="1" t="inlineStr">
@@ -40906,7 +40906,7 @@
       </c>
       <c r="F699" s="1" t="inlineStr">
         <is>
-          <t>regularly</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="G699" s="1" t="inlineStr">
@@ -40964,7 +40964,7 @@
       </c>
       <c r="F700" s="1" t="inlineStr">
         <is>
-          <t>repeat</t>
+          <t>power</t>
         </is>
       </c>
       <c r="G700" s="1" t="inlineStr">
@@ -40999,7 +40999,7 @@
         <v>699</v>
       </c>
       <c r="N700" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="701" ht="30" customHeight="1">
@@ -41022,7 +41022,7 @@
       </c>
       <c r="F701" s="1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>television set</t>
         </is>
       </c>
       <c r="G701" s="1" t="inlineStr">
@@ -41080,7 +41080,7 @@
       </c>
       <c r="F702" s="1" t="inlineStr">
         <is>
-          <t>visual</t>
+          <t>landmark</t>
         </is>
       </c>
       <c r="G702" s="1" t="inlineStr">
@@ -41115,7 +41115,7 @@
         <v>701</v>
       </c>
       <c r="N702" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="703" ht="30" customHeight="1">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="F703" s="1" t="inlineStr">
         <is>
-          <t>mentally</t>
+          <t>contribution</t>
         </is>
       </c>
       <c r="G703" s="1" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="F704" s="1" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>hero</t>
         </is>
       </c>
       <c r="G704" s="1" t="inlineStr">
@@ -41231,7 +41231,7 @@
         <v>703</v>
       </c>
       <c r="N704" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="705" ht="30" customHeight="1">
@@ -41254,7 +41254,7 @@
       </c>
       <c r="F705" s="1" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>pioneer</t>
         </is>
       </c>
       <c r="G705" s="1" t="inlineStr">
@@ -41312,7 +41312,7 @@
       </c>
       <c r="F706" s="1" t="inlineStr">
         <is>
-          <t>especially</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="G706" s="1" t="inlineStr">
@@ -41347,7 +41347,7 @@
         <v>705</v>
       </c>
       <c r="N706" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="707" ht="30" customHeight="1">
@@ -41370,7 +41370,7 @@
       </c>
       <c r="F707" s="1" t="inlineStr">
         <is>
-          <t>diet</t>
+          <t>receive</t>
         </is>
       </c>
       <c r="G707" s="1" t="inlineStr">
@@ -41428,7 +41428,7 @@
       </c>
       <c r="F708" s="1" t="inlineStr">
         <is>
-          <t>maintain</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="G708" s="1" t="inlineStr">
@@ -41486,7 +41486,7 @@
       </c>
       <c r="F709" s="1" t="inlineStr">
         <is>
-          <t>nut</t>
+          <t>award</t>
         </is>
       </c>
       <c r="G709" s="1" t="inlineStr">
@@ -41521,7 +41521,7 @@
         <v>708</v>
       </c>
       <c r="N709" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="710" ht="30" customHeight="1">
@@ -41544,7 +41544,7 @@
       </c>
       <c r="F710" s="1" t="inlineStr">
         <is>
-          <t>relax</t>
+          <t>education</t>
         </is>
       </c>
       <c r="G710" s="1" t="inlineStr">
@@ -41579,7 +41579,7 @@
         <v>709</v>
       </c>
       <c r="N710" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="711" ht="30" customHeight="1">
@@ -41602,7 +41602,7 @@
       </c>
       <c r="F711" s="1" t="inlineStr">
         <is>
-          <t>stressed</t>
+          <t>spend</t>
         </is>
       </c>
       <c r="G711" s="1" t="inlineStr">
@@ -41637,7 +41637,7 @@
         <v>710</v>
       </c>
       <c r="N711" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="712" ht="30" customHeight="1">
@@ -41660,7 +41660,7 @@
       </c>
       <c r="F712" s="1" t="inlineStr">
         <is>
-          <t>tend</t>
+          <t>research</t>
         </is>
       </c>
       <c r="G712" s="1" t="inlineStr">
@@ -41695,7 +41695,7 @@
         <v>711</v>
       </c>
       <c r="N712" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="713" ht="30" customHeight="1">
@@ -41718,7 +41718,7 @@
       </c>
       <c r="F713" s="1" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>achieve</t>
         </is>
       </c>
       <c r="G713" s="1" t="inlineStr">
@@ -41776,7 +41776,7 @@
       </c>
       <c r="F714" s="1" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>well-respected</t>
         </is>
       </c>
       <c r="G714" s="1" t="inlineStr">
@@ -41834,7 +41834,7 @@
       </c>
       <c r="F715" s="1" t="inlineStr">
         <is>
-          <t>fork</t>
+          <t>found</t>
         </is>
       </c>
       <c r="G715" s="1" t="inlineStr">
@@ -41892,7 +41892,7 @@
       </c>
       <c r="F716" s="1" t="inlineStr">
         <is>
-          <t>onion</t>
+          <t>eager</t>
         </is>
       </c>
       <c r="G716" s="1" t="inlineStr">
@@ -41946,7 +41946,7 @@
       </c>
       <c r="F717" s="1" t="inlineStr">
         <is>
-          <t>ant</t>
+          <t>raise</t>
         </is>
       </c>
       <c r="G717" s="1" t="inlineStr">
@@ -41977,7 +41977,7 @@
         <v>716</v>
       </c>
       <c r="N717" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="718" ht="30" customHeight="1">
@@ -42000,7 +42000,7 @@
       </c>
       <c r="F718" s="1" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>mission</t>
         </is>
       </c>
       <c r="G718" s="1" t="inlineStr">
@@ -42058,7 +42058,7 @@
       </c>
       <c r="F719" s="1" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>honour</t>
         </is>
       </c>
       <c r="G719" s="1" t="inlineStr">
@@ -42116,7 +42116,7 @@
       </c>
       <c r="F720" s="1" t="inlineStr">
         <is>
-          <t>sense</t>
+          <t>public</t>
         </is>
       </c>
       <c r="G720" s="1" t="inlineStr">
@@ -42174,7 +42174,7 @@
       </c>
       <c r="F721" s="1" t="inlineStr">
         <is>
-          <t>summary</t>
+          <t>approval</t>
         </is>
       </c>
       <c r="G721" s="1" t="inlineStr">
@@ -42232,7 +42232,7 @@
       </c>
       <c r="F722" s="1" t="inlineStr">
         <is>
-          <t>contain</t>
+          <t>praise</t>
         </is>
       </c>
       <c r="G722" s="1" t="inlineStr">
@@ -42290,7 +42290,7 @@
       </c>
       <c r="F723" s="1" t="inlineStr">
         <is>
-          <t>particular</t>
+          <t>society</t>
         </is>
       </c>
       <c r="G723" s="1" t="inlineStr">
@@ -42325,7 +42325,7 @@
         <v>722</v>
       </c>
       <c r="N723" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724" ht="30" customHeight="1">
@@ -42348,7 +42348,7 @@
       </c>
       <c r="F724" s="1" t="inlineStr">
         <is>
-          <t>chemistry</t>
+          <t>female</t>
         </is>
       </c>
       <c r="G724" s="1" t="inlineStr">
@@ -42402,7 +42402,7 @@
       </c>
       <c r="F725" s="1" t="inlineStr">
         <is>
-          <t>flash card</t>
+          <t>admire</t>
         </is>
       </c>
       <c r="G725" s="1" t="inlineStr">
@@ -42433,7 +42433,7 @@
         <v>724</v>
       </c>
       <c r="N725" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="726" ht="30" customHeight="1">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="F726" s="1" t="inlineStr">
         <is>
-          <t>make a point of doing something</t>
+          <t>inspire</t>
         </is>
       </c>
       <c r="G726" s="1" t="inlineStr">
@@ -42514,7 +42514,7 @@
       </c>
       <c r="F727" s="1" t="inlineStr">
         <is>
-          <t>last but not least</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="G727" s="1" t="inlineStr">
@@ -42572,7 +42572,7 @@
       </c>
       <c r="F728" s="1" t="inlineStr">
         <is>
-          <t>natural disaster</t>
+          <t>feed</t>
         </is>
       </c>
       <c r="G728" s="1" t="inlineStr">
@@ -42603,7 +42603,7 @@
         <v>727</v>
       </c>
       <c r="N728" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="729" ht="30" customHeight="1">
@@ -42626,7 +42626,7 @@
       </c>
       <c r="F729" s="1" t="inlineStr">
         <is>
-          <t>figure out</t>
+          <t>smokejumper</t>
         </is>
       </c>
       <c r="G729" s="1" t="inlineStr">
@@ -42684,7 +42684,7 @@
       </c>
       <c r="F730" s="1" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>thick</t>
         </is>
       </c>
       <c r="G730" s="1" t="inlineStr">
@@ -42719,7 +42719,7 @@
         <v>729</v>
       </c>
       <c r="N730" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="731" ht="30" customHeight="1">
@@ -42742,7 +42742,7 @@
       </c>
       <c r="F731" s="1" t="inlineStr">
         <is>
-          <t>faithful</t>
+          <t>certain</t>
         </is>
       </c>
       <c r="G731" s="1" t="inlineStr">
@@ -42800,7 +42800,7 @@
       </c>
       <c r="F732" s="1" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>kill</t>
         </is>
       </c>
       <c r="G732" s="1" t="inlineStr">
@@ -42835,7 +42835,7 @@
         <v>731</v>
       </c>
       <c r="N732" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="733" ht="30" customHeight="1">
@@ -42858,7 +42858,7 @@
       </c>
       <c r="F733" s="1" t="inlineStr">
         <is>
-          <t>responsible</t>
+          <t>tool</t>
         </is>
       </c>
       <c r="G733" s="1" t="inlineStr">
@@ -42893,7 +42893,7 @@
         <v>732</v>
       </c>
       <c r="N733" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="734" ht="30" customHeight="1">
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F734" s="1" t="inlineStr">
         <is>
-          <t>awake</t>
+          <t>dead</t>
         </is>
       </c>
       <c r="G734" s="1" t="inlineStr">
@@ -42951,7 +42951,7 @@
         <v>733</v>
       </c>
       <c r="N734" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="735" ht="30" customHeight="1">
@@ -42974,7 +42974,7 @@
       </c>
       <c r="F735" s="1" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>brave</t>
         </is>
       </c>
       <c r="G735" s="1" t="inlineStr">
@@ -43009,7 +43009,7 @@
         <v>734</v>
       </c>
       <c r="N735" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="736" ht="30" customHeight="1">
@@ -43032,7 +43032,7 @@
       </c>
       <c r="F736" s="1" t="inlineStr">
         <is>
-          <t>choice</t>
+          <t>tough</t>
         </is>
       </c>
       <c r="G736" s="1" t="inlineStr">
@@ -43090,7 +43090,7 @@
       </c>
       <c r="F737" s="1" t="inlineStr">
         <is>
-          <t>advise</t>
+          <t>fit</t>
         </is>
       </c>
       <c r="G737" s="1" t="inlineStr">
@@ -43148,7 +43148,7 @@
       </c>
       <c r="F738" s="1" t="inlineStr">
         <is>
-          <t>cause</t>
+          <t>otherwise</t>
         </is>
       </c>
       <c r="G738" s="1" t="inlineStr">
@@ -43206,7 +43206,7 @@
       </c>
       <c r="F739" s="1" t="inlineStr">
         <is>
-          <t>complain</t>
+          <t>survive</t>
         </is>
       </c>
       <c r="G739" s="1" t="inlineStr">
@@ -43264,7 +43264,7 @@
       </c>
       <c r="F740" s="1" t="inlineStr">
         <is>
-          <t>litter</t>
+          <t>proud</t>
         </is>
       </c>
       <c r="G740" s="1" t="inlineStr">
@@ -43299,7 +43299,7 @@
         <v>739</v>
       </c>
       <c r="N740" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="741" ht="30" customHeight="1">
@@ -43322,7 +43322,7 @@
       </c>
       <c r="F741" s="1" t="inlineStr">
         <is>
-          <t>unlikely</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="G741" s="1" t="inlineStr">
@@ -43357,7 +43357,7 @@
         <v>740</v>
       </c>
       <c r="N741" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="742" ht="30" customHeight="1">
@@ -43380,7 +43380,7 @@
       </c>
       <c r="F742" s="1" t="inlineStr">
         <is>
-          <t>relieve</t>
+          <t>athlete</t>
         </is>
       </c>
       <c r="G742" s="1" t="inlineStr">
@@ -43438,7 +43438,7 @@
       </c>
       <c r="F743" s="1" t="inlineStr">
         <is>
-          <t>indoors</t>
+          <t>biologist</t>
         </is>
       </c>
       <c r="G743" s="1" t="inlineStr">
@@ -43496,7 +43496,7 @@
       </c>
       <c r="F744" s="1" t="inlineStr">
         <is>
-          <t>magical</t>
+          <t>instrument</t>
         </is>
       </c>
       <c r="G744" s="1" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="F745" s="1" t="inlineStr">
         <is>
-          <t>wealth</t>
+          <t>interest</t>
         </is>
       </c>
       <c r="G745" s="1" t="inlineStr">
@@ -43589,7 +43589,7 @@
         <v>744</v>
       </c>
       <c r="N745" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="746" ht="30" customHeight="1">
@@ -43612,7 +43612,7 @@
       </c>
       <c r="F746" s="1" t="inlineStr">
         <is>
-          <t>queen</t>
+          <t>career</t>
         </is>
       </c>
       <c r="G746" s="1" t="inlineStr">
@@ -43670,7 +43670,7 @@
       </c>
       <c r="F747" s="1" t="inlineStr">
         <is>
-          <t>servant</t>
+          <t>lifetime</t>
         </is>
       </c>
       <c r="G747" s="1" t="inlineStr">
@@ -43705,7 +43705,7 @@
         <v>746</v>
       </c>
       <c r="N747" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="748" ht="30" customHeight="1">
@@ -43728,7 +43728,7 @@
       </c>
       <c r="F748" s="1" t="inlineStr">
         <is>
-          <t>pride</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="G748" s="1" t="inlineStr">
@@ -43786,7 +43786,7 @@
       </c>
       <c r="F749" s="1" t="inlineStr">
         <is>
-          <t>among</t>
+          <t>belt</t>
         </is>
       </c>
       <c r="G749" s="1" t="inlineStr">
@@ -43844,7 +43844,7 @@
       </c>
       <c r="F750" s="1" t="inlineStr">
         <is>
-          <t>relationship</t>
+          <t>shoot</t>
         </is>
       </c>
       <c r="G750" s="1" t="inlineStr">
@@ -43902,7 +43902,7 @@
       </c>
       <c r="F751" s="1" t="inlineStr">
         <is>
-          <t>grow up</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="G751" s="1" t="inlineStr">
@@ -43960,7 +43960,7 @@
       </c>
       <c r="F752" s="1" t="inlineStr">
         <is>
-          <t>care for</t>
+          <t>curious</t>
         </is>
       </c>
       <c r="G752" s="1" t="inlineStr">
@@ -44018,7 +44018,7 @@
       </c>
       <c r="F753" s="1" t="inlineStr">
         <is>
-          <t>in short</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="G753" s="1" t="inlineStr">
@@ -44076,7 +44076,7 @@
       </c>
       <c r="F754" s="1" t="inlineStr">
         <is>
-          <t>have no choice but to do</t>
+          <t>host</t>
         </is>
       </c>
       <c r="G754" s="1" t="inlineStr">
@@ -44134,7 +44134,7 @@
       </c>
       <c r="F755" s="1" t="inlineStr">
         <is>
-          <t>run free</t>
+          <t>beyond</t>
         </is>
       </c>
       <c r="G755" s="1" t="inlineStr">
@@ -44169,7 +44169,7 @@
         <v>754</v>
       </c>
       <c r="N755" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="756" ht="30" customHeight="1">
@@ -44192,7 +44192,7 @@
       </c>
       <c r="F756" s="1" t="inlineStr">
         <is>
-          <t>lie around</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="G756" s="1" t="inlineStr">
@@ -44250,7 +44250,7 @@
       </c>
       <c r="F757" s="1" t="inlineStr">
         <is>
-          <t>complain about</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="G757" s="1" t="inlineStr">
@@ -44308,7 +44308,7 @@
       </c>
       <c r="F758" s="1" t="inlineStr">
         <is>
-          <t>in addition</t>
+          <t>actually</t>
         </is>
       </c>
       <c r="G758" s="1" t="inlineStr">
@@ -44366,7 +44366,7 @@
       </c>
       <c r="F759" s="1" t="inlineStr">
         <is>
-          <t>catch the eye of somebody</t>
+          <t>sail</t>
         </is>
       </c>
       <c r="G759" s="1" t="inlineStr">
@@ -44424,7 +44424,7 @@
       </c>
       <c r="F760" s="1" t="inlineStr">
         <is>
-          <t>elderly</t>
+          <t>ability</t>
         </is>
       </c>
       <c r="G760" s="1" t="inlineStr">
@@ -44459,7 +44459,7 @@
         <v>759</v>
       </c>
       <c r="N760" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="761" ht="30" customHeight="1">
@@ -44482,7 +44482,7 @@
       </c>
       <c r="F761" s="1" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G761" s="1" t="inlineStr">
@@ -44540,7 +44540,7 @@
       </c>
       <c r="F762" s="1" t="inlineStr">
         <is>
-          <t>serious</t>
+          <t>perform</t>
         </is>
       </c>
       <c r="G762" s="1" t="inlineStr">
@@ -44575,7 +44575,7 @@
         <v>761</v>
       </c>
       <c r="N762" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="763" ht="30" customHeight="1">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="F763" s="1" t="inlineStr">
         <is>
-          <t>disease</t>
+          <t>kiss</t>
         </is>
       </c>
       <c r="G763" s="1" t="inlineStr">
@@ -44633,7 +44633,7 @@
         <v>762</v>
       </c>
       <c r="N763" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764" ht="30" customHeight="1">
@@ -44656,7 +44656,7 @@
       </c>
       <c r="F764" s="1" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>hug</t>
         </is>
       </c>
       <c r="G764" s="1" t="inlineStr">
@@ -44691,7 +44691,7 @@
         <v>763</v>
       </c>
       <c r="N764" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="765" ht="30" customHeight="1">
@@ -44714,7 +44714,7 @@
       </c>
       <c r="F765" s="1" t="inlineStr">
         <is>
-          <t>spirits</t>
+          <t>method</t>
         </is>
       </c>
       <c r="G765" s="1" t="inlineStr">
@@ -44772,7 +44772,7 @@
       </c>
       <c r="F766" s="1" t="inlineStr">
         <is>
-          <t>pain</t>
+          <t>compare</t>
         </is>
       </c>
       <c r="G766" s="1" t="inlineStr">
@@ -44830,7 +44830,7 @@
       </c>
       <c r="F767" s="1" t="inlineStr">
         <is>
-          <t>belong</t>
+          <t>nowadays</t>
         </is>
       </c>
       <c r="G767" s="1" t="inlineStr">
@@ -44865,7 +44865,7 @@
         <v>766</v>
       </c>
       <c r="N767" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="768" ht="30" customHeight="1">
@@ -44888,7 +44888,7 @@
       </c>
       <c r="F768" s="1" t="inlineStr">
         <is>
-          <t>spare</t>
+          <t>human being</t>
         </is>
       </c>
       <c r="G768" s="1" t="inlineStr">
@@ -44923,7 +44923,7 @@
         <v>767</v>
       </c>
       <c r="N768" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="769" ht="30" customHeight="1">
@@ -44946,7 +44946,7 @@
       </c>
       <c r="F769" s="1" t="inlineStr">
         <is>
-          <t>volunteer</t>
+          <t>lecture</t>
         </is>
       </c>
       <c r="G769" s="1" t="inlineStr">
@@ -45004,7 +45004,7 @@
       </c>
       <c r="F770" s="1" t="inlineStr">
         <is>
-          <t>joy</t>
+          <t>dinosaur</t>
         </is>
       </c>
       <c r="G770" s="1" t="inlineStr">
@@ -45039,7 +45039,7 @@
         <v>769</v>
       </c>
       <c r="N770" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="771" ht="30" customHeight="1">
@@ -45062,7 +45062,7 @@
       </c>
       <c r="F771" s="1" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>intelligent</t>
         </is>
       </c>
       <c r="G771" s="1" t="inlineStr">
@@ -45097,7 +45097,7 @@
         <v>770</v>
       </c>
       <c r="N771" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="772" ht="30" customHeight="1">
@@ -45120,7 +45120,7 @@
       </c>
       <c r="F772" s="1" t="inlineStr">
         <is>
-          <t>raise</t>
+          <t>talented</t>
         </is>
       </c>
       <c r="G772" s="1" t="inlineStr">
@@ -45155,7 +45155,7 @@
         <v>771</v>
       </c>
       <c r="N772" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="773" ht="30" customHeight="1">
@@ -45178,7 +45178,7 @@
       </c>
       <c r="F773" s="1" t="inlineStr">
         <is>
-          <t>pound</t>
+          <t>artistic</t>
         </is>
       </c>
       <c r="G773" s="1" t="inlineStr">
@@ -45213,7 +45213,7 @@
         <v>772</v>
       </c>
       <c r="N773" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="774" ht="30" customHeight="1">
@@ -45236,7 +45236,7 @@
       </c>
       <c r="F774" s="1" t="inlineStr">
         <is>
-          <t>structure</t>
+          <t>perhaps</t>
         </is>
       </c>
       <c r="G774" s="1" t="inlineStr">
@@ -45271,7 +45271,7 @@
         <v>773</v>
       </c>
       <c r="N774" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="775" ht="30" customHeight="1">
@@ -45294,7 +45294,7 @@
       </c>
       <c r="F775" s="1" t="inlineStr">
         <is>
-          <t>permission</t>
+          <t>notebook</t>
         </is>
       </c>
       <c r="G775" s="1" t="inlineStr">
@@ -45329,7 +45329,7 @@
         <v>774</v>
       </c>
       <c r="N775" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="776" ht="30" customHeight="1">
@@ -45352,7 +45352,7 @@
       </c>
       <c r="F776" s="1" t="inlineStr">
         <is>
-          <t>arrange</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="G776" s="1" t="inlineStr">
@@ -45410,7 +45410,7 @@
       </c>
       <c r="F777" s="1" t="inlineStr">
         <is>
-          <t>donate</t>
+          <t>prehistoric</t>
         </is>
       </c>
       <c r="G777" s="1" t="inlineStr">
@@ -45468,7 +45468,7 @@
       </c>
       <c r="F778" s="1" t="inlineStr">
         <is>
-          <t>mighty</t>
+          <t>completely</t>
         </is>
       </c>
       <c r="G778" s="1" t="inlineStr">
@@ -45526,7 +45526,7 @@
       </c>
       <c r="F779" s="1" t="inlineStr">
         <is>
-          <t>pleasant</t>
+          <t>original</t>
         </is>
       </c>
       <c r="G779" s="1" t="inlineStr">
@@ -45561,7 +45561,7 @@
         <v>778</v>
       </c>
       <c r="N779" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="780" ht="30" customHeight="1">
@@ -45584,7 +45584,7 @@
       </c>
       <c r="F780" s="1" t="inlineStr">
         <is>
-          <t>ease</t>
+          <t>birth</t>
         </is>
       </c>
       <c r="G780" s="1" t="inlineStr">
@@ -45619,7 +45619,7 @@
         <v>779</v>
       </c>
       <c r="N780" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="781" ht="30" customHeight="1">
@@ -45642,7 +45642,7 @@
       </c>
       <c r="F781" s="1" t="inlineStr">
         <is>
-          <t>ache</t>
+          <t>suffering</t>
         </is>
       </c>
       <c r="G781" s="1" t="inlineStr">
@@ -45700,7 +45700,7 @@
       </c>
       <c r="F782" s="1" t="inlineStr">
         <is>
-          <t>voluntary work</t>
+          <t>artist</t>
         </is>
       </c>
       <c r="G782" s="1" t="inlineStr">
@@ -45735,7 +45735,7 @@
         <v>781</v>
       </c>
       <c r="N782" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="783" ht="30" customHeight="1">
@@ -45758,7 +45758,7 @@
       </c>
       <c r="F783" s="1" t="inlineStr">
         <is>
-          <t>disabled people</t>
+          <t>piece</t>
         </is>
       </c>
       <c r="G783" s="1" t="inlineStr">
@@ -45816,7 +45816,7 @@
       </c>
       <c r="F784" s="1" t="inlineStr">
         <is>
-          <t>look after</t>
+          <t>death</t>
         </is>
       </c>
       <c r="G784" s="1" t="inlineStr">
@@ -45851,7 +45851,7 @@
         <v>783</v>
       </c>
       <c r="N784" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="785" ht="30" customHeight="1">
@@ -45874,7 +45874,7 @@
       </c>
       <c r="F785" s="1" t="inlineStr">
         <is>
-          <t>suffer from</t>
+          <t>whole</t>
         </is>
       </c>
       <c r="G785" s="1" t="inlineStr">
@@ -45909,7 +45909,7 @@
         <v>784</v>
       </c>
       <c r="N785" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="786" ht="30" customHeight="1">
@@ -45932,7 +45932,7 @@
       </c>
       <c r="F786" s="1" t="inlineStr">
         <is>
-          <t>cheer somebody up</t>
+          <t>editor</t>
         </is>
       </c>
       <c r="G786" s="1" t="inlineStr">
@@ -45990,7 +45990,7 @@
       </c>
       <c r="F787" s="1" t="inlineStr">
         <is>
-          <t>raise one's spirits</t>
+          <t>organize</t>
         </is>
       </c>
       <c r="G787" s="1" t="inlineStr">
@@ -46048,7 +46048,7 @@
       </c>
       <c r="F788" s="1" t="inlineStr">
         <is>
-          <t>in low spirits</t>
+          <t>order</t>
         </is>
       </c>
       <c r="G788" s="1" t="inlineStr">
@@ -46106,7 +46106,7 @@
       </c>
       <c r="F789" s="1" t="inlineStr">
         <is>
-          <t>in order to</t>
+          <t>record</t>
         </is>
       </c>
       <c r="G789" s="1" t="inlineStr">
@@ -46141,7 +46141,7 @@
         <v>788</v>
       </c>
       <c r="N789" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="790" ht="30" customHeight="1">
@@ -46164,7 +46164,7 @@
       </c>
       <c r="F790" s="1" t="inlineStr">
         <is>
-          <t>in need</t>
+          <t>die out</t>
         </is>
       </c>
       <c r="G790" s="1" t="inlineStr">
@@ -46199,7 +46199,7 @@
         <v>789</v>
       </c>
       <c r="N790" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="791" ht="30" customHeight="1">
@@ -46222,7 +46222,7 @@
       </c>
       <c r="F791" s="1" t="inlineStr">
         <is>
-          <t>flower arranging</t>
+          <t>a type of</t>
         </is>
       </c>
       <c r="G791" s="1" t="inlineStr">
@@ -46280,7 +46280,7 @@
       </c>
       <c r="F792" s="1" t="inlineStr">
         <is>
-          <t>tidy up</t>
+          <t>be related to</t>
         </is>
       </c>
       <c r="G792" s="1" t="inlineStr">
@@ -46338,7 +46338,7 @@
       </c>
       <c r="F793" s="1" t="inlineStr">
         <is>
-          <t>in vain</t>
+          <t>general education</t>
         </is>
       </c>
       <c r="G793" s="1" t="inlineStr">
@@ -46396,7 +46396,7 @@
       </c>
       <c r="F794" s="1" t="inlineStr">
         <is>
-          <t>shake</t>
+          <t>go back a long way</t>
         </is>
       </c>
       <c r="G794" s="1" t="inlineStr">
@@ -46454,7 +46454,7 @@
       </c>
       <c r="F795" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>be similar to</t>
         </is>
       </c>
       <c r="G795" s="1" t="inlineStr">
@@ -46512,7 +46512,7 @@
       </c>
       <c r="F796" s="1" t="inlineStr">
         <is>
-          <t>madam</t>
+          <t>alphabetical order</t>
         </is>
       </c>
       <c r="G796" s="1" t="inlineStr">
@@ -46570,7 +46570,7 @@
       </c>
       <c r="F797" s="1" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>play an important role</t>
         </is>
       </c>
       <c r="G797" s="1" t="inlineStr">
@@ -46628,7 +46628,7 @@
       </c>
       <c r="F798" s="1" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>flight</t>
         </is>
       </c>
       <c r="G798" s="1" t="inlineStr">
@@ -46686,7 +46686,7 @@
       </c>
       <c r="F799" s="1" t="inlineStr">
         <is>
-          <t>impression</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="G799" s="1" t="inlineStr">
@@ -46744,7 +46744,7 @@
       </c>
       <c r="F800" s="1" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>everywhere</t>
         </is>
       </c>
       <c r="G800" s="1" t="inlineStr">
@@ -46802,7 +46802,7 @@
       </c>
       <c r="F801" s="1" t="inlineStr">
         <is>
-          <t>observe</t>
+          <t>challenge</t>
         </is>
       </c>
       <c r="G801" s="1" t="inlineStr">
@@ -46860,7 +46860,7 @@
       </c>
       <c r="F802" s="1" t="inlineStr">
         <is>
-          <t>remind</t>
+          <t>prize</t>
         </is>
       </c>
       <c r="G802" s="1" t="inlineStr">
@@ -46918,7 +46918,7 @@
       </c>
       <c r="F803" s="1" t="inlineStr">
         <is>
-          <t>ballet</t>
+          <t>promise</t>
         </is>
       </c>
       <c r="G803" s="1" t="inlineStr">
@@ -46976,7 +46976,7 @@
       </c>
       <c r="F804" s="1" t="inlineStr">
         <is>
-          <t>emphasize</t>
+          <t>chessboard</t>
         </is>
       </c>
       <c r="G804" s="1" t="inlineStr">
@@ -47034,7 +47034,7 @@
       </c>
       <c r="F805" s="1" t="inlineStr">
         <is>
-          <t>nod</t>
+          <t>silver</t>
         </is>
       </c>
       <c r="G805" s="1" t="inlineStr">
@@ -47092,7 +47092,7 @@
       </c>
       <c r="F806" s="1" t="inlineStr">
         <is>
-          <t>meaning</t>
+          <t>reply</t>
         </is>
       </c>
       <c r="G806" s="1" t="inlineStr">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="F807" s="1" t="inlineStr">
         <is>
-          <t>immediately</t>
+          <t>hesitation</t>
         </is>
       </c>
       <c r="G807" s="1" t="inlineStr">
@@ -47208,7 +47208,7 @@
       </c>
       <c r="F808" s="1" t="inlineStr">
         <is>
-          <t>shy</t>
+          <t>wonder</t>
         </is>
       </c>
       <c r="G808" s="1" t="inlineStr">
@@ -47266,7 +47266,7 @@
       </c>
       <c r="F809" s="1" t="inlineStr">
         <is>
-          <t>case</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="G809" s="1" t="inlineStr">
@@ -47324,7 +47324,7 @@
       </c>
       <c r="F810" s="1" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="G810" s="1" t="inlineStr">
@@ -47382,7 +47382,7 @@
       </c>
       <c r="F811" s="1" t="inlineStr">
         <is>
-          <t>truly</t>
+          <t>currently</t>
         </is>
       </c>
       <c r="G811" s="1" t="inlineStr">
@@ -47440,7 +47440,7 @@
       </c>
       <c r="F812" s="1" t="inlineStr">
         <is>
-          <t>suppose</t>
+          <t>check</t>
         </is>
       </c>
       <c r="G812" s="1" t="inlineStr">
@@ -47498,7 +47498,7 @@
       </c>
       <c r="F813" s="1" t="inlineStr">
         <is>
-          <t>behaviour</t>
+          <t>budget</t>
         </is>
       </c>
       <c r="G813" s="1" t="inlineStr">
@@ -47556,7 +47556,7 @@
       </c>
       <c r="F814" s="1" t="inlineStr">
         <is>
-          <t>uncomfortable</t>
+          <t>province</t>
         </is>
       </c>
       <c r="G814" s="1" t="inlineStr">
@@ -47614,7 +47614,7 @@
       </c>
       <c r="F815" s="1" t="inlineStr">
         <is>
-          <t>hold something up</t>
+          <t>sharply</t>
         </is>
       </c>
       <c r="G815" s="1" t="inlineStr">
@@ -47672,7 +47672,7 @@
       </c>
       <c r="F816" s="1" t="inlineStr">
         <is>
-          <t>sit up</t>
+          <t>count</t>
         </is>
       </c>
       <c r="G816" s="1" t="inlineStr">
@@ -47730,7 +47730,7 @@
       </c>
       <c r="F817" s="1" t="inlineStr">
         <is>
-          <t>make a good impression on</t>
+          <t>system</t>
         </is>
       </c>
       <c r="G817" s="1" t="inlineStr">
@@ -47788,7 +47788,7 @@
       </c>
       <c r="F818" s="1" t="inlineStr">
         <is>
-          <t>eye contact</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="G818" s="1" t="inlineStr">
@@ -47846,7 +47846,7 @@
       </c>
       <c r="F819" s="1" t="inlineStr">
         <is>
-          <t>pay attention</t>
+          <t>represent</t>
         </is>
       </c>
       <c r="G819" s="1" t="inlineStr">
@@ -47904,7 +47904,7 @@
       </c>
       <c r="F820" s="1" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>exactly</t>
         </is>
       </c>
       <c r="G820" s="1" t="inlineStr">
@@ -47962,7 +47962,7 @@
       </c>
       <c r="F821" s="1" t="inlineStr">
         <is>
-          <t>combine</t>
+          <t>flight schedule</t>
         </is>
       </c>
       <c r="G821" s="1" t="inlineStr">
@@ -48020,7 +48020,7 @@
       </c>
       <c r="F822" s="1" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>price tag</t>
         </is>
       </c>
       <c r="G822" s="1" t="inlineStr">
@@ -48078,7 +48078,7 @@
       </c>
       <c r="F823" s="1" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>for a moment</t>
         </is>
       </c>
       <c r="G823" s="1" t="inlineStr">
@@ -48136,7 +48136,7 @@
       </c>
       <c r="F824" s="1" t="inlineStr">
         <is>
-          <t>artificial intelligence</t>
+          <t>without hesitation</t>
         </is>
       </c>
       <c r="G824" s="1" t="inlineStr">
@@ -48194,7 +48194,7 @@
       </c>
       <c r="F825" s="1" t="inlineStr">
         <is>
-          <t>hero</t>
+          <t>go up</t>
         </is>
       </c>
       <c r="G825" s="1" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="F826" s="1" t="inlineStr">
         <is>
-          <t>classic</t>
+          <t>go down</t>
         </is>
       </c>
       <c r="G826" s="1" t="inlineStr">
@@ -48310,7 +48310,7 @@
       </c>
       <c r="F827" s="1" t="inlineStr">
         <is>
-          <t>speech</t>
+          <t>write down</t>
         </is>
       </c>
       <c r="G827" s="1" t="inlineStr">
@@ -48368,7 +48368,7 @@
       </c>
       <c r="F828" s="1" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>instead of</t>
         </is>
       </c>
       <c r="G828" s="1" t="inlineStr">
@@ -48426,7 +48426,7 @@
       </c>
       <c r="F829" s="1" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G829" s="1" t="inlineStr">
@@ -48484,7 +48484,7 @@
       </c>
       <c r="F830" s="1" t="inlineStr">
         <is>
-          <t>mind</t>
+          <t>flood</t>
         </is>
       </c>
       <c r="G830" s="1" t="inlineStr">
@@ -48542,7 +48542,7 @@
       </c>
       <c r="F831" s="1" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>multimedia</t>
         </is>
       </c>
       <c r="G831" s="1" t="inlineStr">
@@ -48600,7 +48600,7 @@
       </c>
       <c r="F832" s="1" t="inlineStr">
         <is>
-          <t>crash</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="G832" s="1" t="inlineStr">
@@ -48658,7 +48658,7 @@
       </c>
       <c r="F833" s="1" t="inlineStr">
         <is>
-          <t>wave</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="G833" s="1" t="inlineStr">
@@ -48716,7 +48716,7 @@
       </c>
       <c r="F834" s="1" t="inlineStr">
         <is>
-          <t>folk</t>
+          <t>payment</t>
         </is>
       </c>
       <c r="G834" s="1" t="inlineStr">
@@ -48774,7 +48774,7 @@
       </c>
       <c r="F835" s="1" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>warn</t>
         </is>
       </c>
       <c r="G835" s="1" t="inlineStr">
@@ -48832,7 +48832,7 @@
       </c>
       <c r="F836" s="1" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>treatment</t>
         </is>
       </c>
       <c r="G836" s="1" t="inlineStr">
@@ -48890,7 +48890,7 @@
       </c>
       <c r="F837" s="1" t="inlineStr">
         <is>
-          <t>advantage</t>
+          <t>data</t>
         </is>
       </c>
       <c r="G837" s="1" t="inlineStr">
@@ -48948,7 +48948,7 @@
       </c>
       <c r="F838" s="1" t="inlineStr">
         <is>
-          <t>breath</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G838" s="1" t="inlineStr">
@@ -49006,7 +49006,7 @@
       </c>
       <c r="F839" s="1" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="G839" s="1" t="inlineStr">
@@ -49064,7 +49064,7 @@
       </c>
       <c r="F840" s="1" t="inlineStr">
         <is>
-          <t>shadow puppet</t>
+          <t>flow</t>
         </is>
       </c>
       <c r="G840" s="1" t="inlineStr">
@@ -49122,7 +49122,7 @@
       </c>
       <c r="F841" s="1" t="inlineStr">
         <is>
-          <t>ink-wash painting</t>
+          <t>smoothly</t>
         </is>
       </c>
       <c r="G841" s="1" t="inlineStr">
@@ -49180,7 +49180,7 @@
       </c>
       <c r="F842" s="1" t="inlineStr">
         <is>
-          <t>come to life</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="G842" s="1" t="inlineStr">
@@ -49238,7 +49238,7 @@
       </c>
       <c r="F843" s="1" t="inlineStr">
         <is>
-          <t>with the help of</t>
+          <t>screen</t>
         </is>
       </c>
       <c r="G843" s="1" t="inlineStr">
@@ -49296,7 +49296,7 @@
       </c>
       <c r="F844" s="1" t="inlineStr">
         <is>
-          <t>comic strip</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="G844" s="1" t="inlineStr">
@@ -49354,7 +49354,7 @@
       </c>
       <c r="F845" s="1" t="inlineStr">
         <is>
-          <t>watch out</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="G845" s="1" t="inlineStr">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="F846" s="1" t="inlineStr">
         <is>
-          <t>look out</t>
+          <t>social</t>
         </is>
       </c>
       <c r="G846" s="1" t="inlineStr">
@@ -49470,7 +49470,7 @@
       </c>
       <c r="F847" s="1" t="inlineStr">
         <is>
-          <t>weather forecast</t>
+          <t>message</t>
         </is>
       </c>
       <c r="G847" s="1" t="inlineStr">
@@ -49528,7 +49528,7 @@
       </c>
       <c r="F848" s="1" t="inlineStr">
         <is>
-          <t>life jacket</t>
+          <t>interview</t>
         </is>
       </c>
       <c r="G848" s="1" t="inlineStr">
@@ -49586,7 +49586,7 @@
       </c>
       <c r="F849" s="1" t="inlineStr">
         <is>
-          <t>thank goodness</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="G849" s="1" t="inlineStr">
@@ -49644,7 +49644,7 @@
       </c>
       <c r="F850" s="1" t="inlineStr">
         <is>
-          <t>make it</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="G850" s="1" t="inlineStr">
@@ -49702,7 +49702,7 @@
       </c>
       <c r="F851" s="1" t="inlineStr">
         <is>
-          <t>date back</t>
+          <t>effect</t>
         </is>
       </c>
       <c r="G851" s="1" t="inlineStr">
@@ -49760,7 +49760,7 @@
       </c>
       <c r="F852" s="1" t="inlineStr">
         <is>
-          <t>have an influence on</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="G852" s="1" t="inlineStr">
@@ -49818,7 +49818,7 @@
       </c>
       <c r="F853" s="1" t="inlineStr">
         <is>
-          <t>folk art</t>
+          <t>novel</t>
         </is>
       </c>
       <c r="G853" s="1" t="inlineStr">
@@ -49876,7 +49876,7 @@
       </c>
       <c r="F854" s="1" t="inlineStr">
         <is>
-          <t>at risk of</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="G854" s="1" t="inlineStr">
@@ -49934,7 +49934,7 @@
       </c>
       <c r="F855" s="1" t="inlineStr">
         <is>
-          <t>in the shape of</t>
+          <t>basis</t>
         </is>
       </c>
       <c r="G855" s="1" t="inlineStr">
@@ -49992,7 +49992,7 @@
       </c>
       <c r="F856" s="1" t="inlineStr">
         <is>
-          <t>take one's eyes off something</t>
+          <t>microprocessor</t>
         </is>
       </c>
       <c r="G856" s="1" t="inlineStr">
@@ -50050,7 +50050,7 @@
       </c>
       <c r="F857" s="1" t="inlineStr">
         <is>
-          <t>hold one's breath</t>
+          <t>microchip</t>
         </is>
       </c>
       <c r="G857" s="1" t="inlineStr">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="F858" s="1" t="inlineStr">
         <is>
-          <t>neither ... nor ...</t>
+          <t>major</t>
         </is>
       </c>
       <c r="G858" s="1" t="inlineStr">
@@ -50166,7 +50166,7 @@
       </c>
       <c r="F859" s="1" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>breakthrough</t>
         </is>
       </c>
       <c r="G859" s="1" t="inlineStr">
@@ -50224,7 +50224,7 @@
       </c>
       <c r="F860" s="1" t="inlineStr">
         <is>
-          <t>masterpiece</t>
+          <t>electronic</t>
         </is>
       </c>
       <c r="G860" s="1" t="inlineStr">
@@ -50282,7 +50282,7 @@
       </c>
       <c r="F861" s="1" t="inlineStr">
         <is>
-          <t>whenever</t>
+          <t>software</t>
         </is>
       </c>
       <c r="G861" s="1" t="inlineStr">
@@ -50340,7 +50340,7 @@
       </c>
       <c r="F862" s="1" t="inlineStr">
         <is>
-          <t>alone</t>
+          <t>app</t>
         </is>
       </c>
       <c r="G862" s="1" t="inlineStr">
@@ -50398,7 +50398,7 @@
       </c>
       <c r="F863" s="1" t="inlineStr">
         <is>
-          <t>copy</t>
+          <t>era</t>
         </is>
       </c>
       <c r="G863" s="1" t="inlineStr">
@@ -50456,7 +50456,7 @@
       </c>
       <c r="F864" s="1" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>download</t>
         </is>
       </c>
       <c r="G864" s="1" t="inlineStr">
@@ -50514,7 +50514,7 @@
       </c>
       <c r="F865" s="1" t="inlineStr">
         <is>
-          <t>separate</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="G865" s="1" t="inlineStr">
@@ -50572,7 +50572,7 @@
       </c>
       <c r="F866" s="1" t="inlineStr">
         <is>
-          <t>exhibition</t>
+          <t>connect to</t>
         </is>
       </c>
       <c r="G866" s="1" t="inlineStr">
@@ -50630,7 +50630,7 @@
       </c>
       <c r="F867" s="1" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>bring big changes to</t>
         </is>
       </c>
       <c r="G867" s="1" t="inlineStr">
@@ -50688,7 +50688,7 @@
       </c>
       <c r="F868" s="1" t="inlineStr">
         <is>
-          <t>detail</t>
+          <t>mobile payment</t>
         </is>
       </c>
       <c r="G868" s="1" t="inlineStr">
@@ -50746,7 +50746,7 @@
       </c>
       <c r="F869" s="1" t="inlineStr">
         <is>
-          <t>require</t>
+          <t>take...for example</t>
         </is>
       </c>
       <c r="G869" s="1" t="inlineStr">
@@ -50804,7 +50804,7 @@
       </c>
       <c r="F870" s="1" t="inlineStr">
         <is>
-          <t>daughter</t>
+          <t>rubbish bin</t>
         </is>
       </c>
       <c r="G870" s="1" t="inlineStr">
@@ -50862,7 +50862,7 @@
       </c>
       <c r="F871" s="1" t="inlineStr">
         <is>
-          <t>priceless</t>
+          <t>social media</t>
         </is>
       </c>
       <c r="G871" s="1" t="inlineStr">
@@ -50920,7 +50920,7 @@
       </c>
       <c r="F872" s="1" t="inlineStr">
         <is>
-          <t>sculpture</t>
+          <t>in person</t>
         </is>
       </c>
       <c r="G872" s="1" t="inlineStr">
@@ -50978,7 +50978,7 @@
       </c>
       <c r="F873" s="1" t="inlineStr">
         <is>
-          <t>unfortunately</t>
+          <t>the general public</t>
         </is>
       </c>
       <c r="G873" s="1" t="inlineStr">
@@ -51036,7 +51036,7 @@
       </c>
       <c r="F874" s="1" t="inlineStr">
         <is>
-          <t>graduate</t>
+          <t>balloon</t>
         </is>
       </c>
       <c r="G874" s="1" t="inlineStr">
@@ -51094,7 +51094,7 @@
       </c>
       <c r="F875" s="1" t="inlineStr">
         <is>
-          <t>limit</t>
+          <t>wheel</t>
         </is>
       </c>
       <c r="G875" s="1" t="inlineStr">
@@ -51152,7 +51152,7 @@
       </c>
       <c r="F876" s="1" t="inlineStr">
         <is>
-          <t>temperature</t>
+          <t>central</t>
         </is>
       </c>
       <c r="G876" s="1" t="inlineStr">
@@ -51210,7 +51210,7 @@
       </c>
       <c r="F877" s="1" t="inlineStr">
         <is>
-          <t>preserve</t>
+          <t>although</t>
         </is>
       </c>
       <c r="G877" s="1" t="inlineStr">
@@ -51268,7 +51268,7 @@
       </c>
       <c r="F878" s="1" t="inlineStr">
         <is>
-          <t>in one sitting</t>
+          <t>attach</t>
         </is>
       </c>
       <c r="G878" s="1" t="inlineStr">
@@ -51326,7 +51326,7 @@
       </c>
       <c r="F879" s="1" t="inlineStr">
         <is>
-          <t>in the mood</t>
+          <t>pull</t>
         </is>
       </c>
       <c r="G879" s="1" t="inlineStr">
@@ -51384,7 +51384,7 @@
       </c>
       <c r="F880" s="1" t="inlineStr">
         <is>
-          <t>pass along</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G880" s="1" t="inlineStr">
@@ -51442,7 +51442,7 @@
       </c>
       <c r="F881" s="1" t="inlineStr">
         <is>
-          <t>be at one with ...</t>
+          <t>path</t>
         </is>
       </c>
       <c r="G881" s="1" t="inlineStr">
@@ -51500,7 +51500,7 @@
       </c>
       <c r="F882" s="1" t="inlineStr">
         <is>
-          <t>next to</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="G882" s="1" t="inlineStr">
@@ -51558,7 +51558,7 @@
       </c>
       <c r="F883" s="1" t="inlineStr">
         <is>
-          <t>at last</t>
+          <t>depend</t>
         </is>
       </c>
       <c r="G883" s="1" t="inlineStr">
@@ -51616,7 +51616,7 @@
       </c>
       <c r="F884" s="1" t="inlineStr">
         <is>
-          <t>all walks of life</t>
+          <t>doubt</t>
         </is>
       </c>
       <c r="G884" s="1" t="inlineStr">
@@ -51674,7 +51674,7 @@
       </c>
       <c r="F885" s="1" t="inlineStr">
         <is>
-          <t>all the time</t>
+          <t>personally</t>
         </is>
       </c>
       <c r="G885" s="1" t="inlineStr">
@@ -51732,7 +51732,7 @@
       </c>
       <c r="F886" s="1" t="inlineStr">
         <is>
-          <t>make up one's mind</t>
+          <t>prediction</t>
         </is>
       </c>
       <c r="G886" s="1" t="inlineStr">
@@ -51790,7 +51790,7 @@
       </c>
       <c r="F887" s="1" t="inlineStr">
         <is>
-          <t>recognize</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="G887" s="1" t="inlineStr">
@@ -51848,7 +51848,7 @@
       </c>
       <c r="F888" s="1" t="inlineStr">
         <is>
-          <t>mirror</t>
+          <t>benefit</t>
         </is>
       </c>
       <c r="G888" s="1" t="inlineStr">
@@ -51902,11 +51902,11 @@
         <v>5</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F889" s="1" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>wing</t>
         </is>
       </c>
       <c r="G889" s="1" t="inlineStr">
@@ -51941,7 +51941,7 @@
         <v>888</v>
       </c>
       <c r="N889" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="890" ht="30" customHeight="1">
@@ -51960,11 +51960,11 @@
         <v>5</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F890" s="1" t="inlineStr">
         <is>
-          <t>honest</t>
+          <t>distance</t>
         </is>
       </c>
       <c r="G890" s="1" t="inlineStr">
@@ -51999,7 +51999,7 @@
         <v>889</v>
       </c>
       <c r="N890" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="891" ht="30" customHeight="1">
@@ -52022,7 +52022,7 @@
       </c>
       <c r="F891" s="1" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>petrol</t>
         </is>
       </c>
       <c r="G891" s="1" t="inlineStr">
@@ -52057,7 +52057,7 @@
         <v>890</v>
       </c>
       <c r="N891" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="892" ht="30" customHeight="1">
@@ -52080,7 +52080,7 @@
       </c>
       <c r="F892" s="1" t="inlineStr">
         <is>
-          <t>improve</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="G892" s="1" t="inlineStr">
@@ -52115,7 +52115,7 @@
         <v>891</v>
       </c>
       <c r="N892" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="893" ht="30" customHeight="1">
@@ -52138,7 +52138,7 @@
       </c>
       <c r="F893" s="1" t="inlineStr">
         <is>
-          <t>confident</t>
+          <t>anywhere</t>
         </is>
       </c>
       <c r="G893" s="1" t="inlineStr">
@@ -52173,7 +52173,7 @@
         <v>892</v>
       </c>
       <c r="N893" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="894" ht="30" customHeight="1">
@@ -52196,7 +52196,7 @@
       </c>
       <c r="F894" s="1" t="inlineStr">
         <is>
-          <t>courage</t>
+          <t>notice</t>
         </is>
       </c>
       <c r="G894" s="1" t="inlineStr">
@@ -52231,7 +52231,7 @@
         <v>893</v>
       </c>
       <c r="N894" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="895" ht="30" customHeight="1">
@@ -52254,7 +52254,7 @@
       </c>
       <c r="F895" s="1" t="inlineStr">
         <is>
-          <t>friendship</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G895" s="1" t="inlineStr">
@@ -52289,7 +52289,7 @@
         <v>894</v>
       </c>
       <c r="N895" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="896" ht="30" customHeight="1">
@@ -52312,7 +52312,7 @@
       </c>
       <c r="F896" s="1" t="inlineStr">
         <is>
-          <t>admiration</t>
+          <t>mixture</t>
         </is>
       </c>
       <c r="G896" s="1" t="inlineStr">
@@ -52347,7 +52347,7 @@
         <v>895</v>
       </c>
       <c r="N896" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="897" ht="30" customHeight="1">
@@ -52370,7 +52370,7 @@
       </c>
       <c r="F897" s="1" t="inlineStr">
         <is>
-          <t>respect</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="G897" s="1" t="inlineStr">
@@ -52405,7 +52405,7 @@
         <v>896</v>
       </c>
       <c r="N897" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="898" ht="30" customHeight="1">
@@ -52428,7 +52428,7 @@
       </c>
       <c r="F898" s="1" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>press</t>
         </is>
       </c>
       <c r="G898" s="1" t="inlineStr">
@@ -52463,7 +52463,7 @@
         <v>897</v>
       </c>
       <c r="N898" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="899" ht="30" customHeight="1">
@@ -52486,7 +52486,7 @@
       </c>
       <c r="F899" s="1" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="G899" s="1" t="inlineStr">
@@ -52521,7 +52521,7 @@
         <v>898</v>
       </c>
       <c r="N899" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="900" ht="30" customHeight="1">
@@ -52544,7 +52544,7 @@
       </c>
       <c r="F900" s="1" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>steam locomotive</t>
         </is>
       </c>
       <c r="G900" s="1" t="inlineStr">
@@ -52579,7 +52579,7 @@
         <v>899</v>
       </c>
       <c r="N900" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="901" ht="30" customHeight="1">
@@ -52602,7 +52602,7 @@
       </c>
       <c r="F901" s="1" t="inlineStr">
         <is>
-          <t>personal</t>
+          <t>crewed spacecraft</t>
         </is>
       </c>
       <c r="G901" s="1" t="inlineStr">
@@ -52637,7 +52637,7 @@
         <v>900</v>
       </c>
       <c r="N901" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="902" ht="30" customHeight="1">
@@ -52660,7 +52660,7 @@
       </c>
       <c r="F902" s="1" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>on foot</t>
         </is>
       </c>
       <c r="G902" s="1" t="inlineStr">
@@ -52695,7 +52695,7 @@
         <v>901</v>
       </c>
       <c r="N902" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="903" ht="30" customHeight="1">
@@ -52718,7 +52718,7 @@
       </c>
       <c r="F903" s="1" t="inlineStr">
         <is>
-          <t>caring</t>
+          <t>a number of</t>
         </is>
       </c>
       <c r="G903" s="1" t="inlineStr">
@@ -52753,7 +52753,7 @@
         <v>902</v>
       </c>
       <c r="N903" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="904" ht="30" customHeight="1">
@@ -52776,7 +52776,7 @@
       </c>
       <c r="F904" s="1" t="inlineStr">
         <is>
-          <t>describe</t>
+          <t>take place</t>
         </is>
       </c>
       <c r="G904" s="1" t="inlineStr">
@@ -52811,7 +52811,7 @@
         <v>903</v>
       </c>
       <c r="N904" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="905" ht="30" customHeight="1">
@@ -52834,7 +52834,7 @@
       </c>
       <c r="F905" s="1" t="inlineStr">
         <is>
-          <t>appearance</t>
+          <t>for instance</t>
         </is>
       </c>
       <c r="G905" s="1" t="inlineStr">
@@ -52869,7 +52869,7 @@
         <v>904</v>
       </c>
       <c r="N905" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="906" ht="30" customHeight="1">
@@ -52892,7 +52892,7 @@
       </c>
       <c r="F906" s="1" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>large amounts of</t>
         </is>
       </c>
       <c r="G906" s="1" t="inlineStr">
@@ -52927,7 +52927,7 @@
         <v>905</v>
       </c>
       <c r="N906" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="907" ht="30" customHeight="1">
@@ -52950,7 +52950,7 @@
       </c>
       <c r="F907" s="1" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>international trade</t>
         </is>
       </c>
       <c r="G907" s="1" t="inlineStr">
@@ -52985,7 +52985,7 @@
         <v>906</v>
       </c>
       <c r="N907" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="908" ht="30" customHeight="1">
@@ -53008,7 +53008,7 @@
       </c>
       <c r="F908" s="1" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>depend on</t>
         </is>
       </c>
       <c r="G908" s="1" t="inlineStr">
@@ -53043,7 +53043,7 @@
         <v>907</v>
       </c>
       <c r="N908" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="909" ht="30" customHeight="1">
@@ -53066,7 +53066,7 @@
       </c>
       <c r="F909" s="1" t="inlineStr">
         <is>
-          <t>basic</t>
+          <t>3D printer</t>
         </is>
       </c>
       <c r="G909" s="1" t="inlineStr">
@@ -53101,7 +53101,7 @@
         <v>908</v>
       </c>
       <c r="N909" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="910" ht="30" customHeight="1">
@@ -53124,7 +53124,7 @@
       </c>
       <c r="F910" s="1" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>without doubt</t>
         </is>
       </c>
       <c r="G910" s="1" t="inlineStr">
@@ -53159,7 +53159,7 @@
         <v>909</v>
       </c>
       <c r="N910" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="911" ht="30" customHeight="1">
@@ -53182,7 +53182,7 @@
       </c>
       <c r="F911" s="1" t="inlineStr">
         <is>
-          <t>however</t>
+          <t>of all time</t>
         </is>
       </c>
       <c r="G911" s="1" t="inlineStr">
@@ -53217,7 +53217,7 @@
         <v>910</v>
       </c>
       <c r="N911" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="912" ht="30" customHeight="1">
@@ -53240,7 +53240,7 @@
       </c>
       <c r="F912" s="1" t="inlineStr">
         <is>
-          <t>glad</t>
+          <t>make fun of</t>
         </is>
       </c>
       <c r="G912" s="1" t="inlineStr">
@@ -53275,7 +53275,7 @@
         <v>911</v>
       </c>
       <c r="N912" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="913" ht="30" customHeight="1">
@@ -53298,7 +53298,7 @@
       </c>
       <c r="F913" s="1" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>traffic jam</t>
         </is>
       </c>
       <c r="G913" s="1" t="inlineStr">
@@ -53333,7 +53333,7 @@
         <v>912</v>
       </c>
       <c r="N913" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="914" ht="30" customHeight="1">
@@ -53356,7 +53356,7 @@
       </c>
       <c r="F914" s="1" t="inlineStr">
         <is>
-          <t>end</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="G914" s="1" t="inlineStr">
@@ -53391,7 +53391,7 @@
         <v>913</v>
       </c>
       <c r="N914" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="915" ht="30" customHeight="1">
@@ -53414,7 +53414,7 @@
       </c>
       <c r="F915" s="1" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>nervous</t>
         </is>
       </c>
       <c r="G915" s="1" t="inlineStr">
@@ -53449,7 +53449,7 @@
         <v>914</v>
       </c>
       <c r="N915" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="916" ht="30" customHeight="1">
@@ -53472,7 +53472,7 @@
       </c>
       <c r="F916" s="1" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>grateful</t>
         </is>
       </c>
       <c r="G916" s="1" t="inlineStr">
@@ -53507,7 +53507,7 @@
         <v>915</v>
       </c>
       <c r="N916" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="917" ht="30" customHeight="1">
@@ -53530,7 +53530,7 @@
       </c>
       <c r="F917" s="1" t="inlineStr">
         <is>
-          <t>corner</t>
+          <t>chopstick</t>
         </is>
       </c>
       <c r="G917" s="1" t="inlineStr">
@@ -53565,7 +53565,7 @@
         <v>916</v>
       </c>
       <c r="N917" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="918" ht="30" customHeight="1">
@@ -53588,7 +53588,7 @@
       </c>
       <c r="F918" s="1" t="inlineStr">
         <is>
-          <t>activity</t>
+          <t>tour</t>
         </is>
       </c>
       <c r="G918" s="1" t="inlineStr">
@@ -53623,7 +53623,7 @@
         <v>917</v>
       </c>
       <c r="N918" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="919" ht="30" customHeight="1">
@@ -53646,7 +53646,7 @@
       </c>
       <c r="F919" s="1" t="inlineStr">
         <is>
-          <t>club</t>
+          <t>tai chi</t>
         </is>
       </c>
       <c r="G919" s="1" t="inlineStr">
@@ -53681,7 +53681,7 @@
         <v>918</v>
       </c>
       <c r="N919" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="920" ht="30" customHeight="1">
@@ -53704,7 +53704,7 @@
       </c>
       <c r="F920" s="1" t="inlineStr">
         <is>
-          <t>practise</t>
+          <t>yet</t>
         </is>
       </c>
       <c r="G920" s="1" t="inlineStr">
@@ -53739,7 +53739,7 @@
         <v>919</v>
       </c>
       <c r="N920" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="921" ht="30" customHeight="1">
@@ -53762,7 +53762,7 @@
       </c>
       <c r="F921" s="1" t="inlineStr">
         <is>
-          <t>solve</t>
+          <t>independent</t>
         </is>
       </c>
       <c r="G921" s="1" t="inlineStr">
@@ -53797,7 +53797,7 @@
         <v>920</v>
       </c>
       <c r="N921" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="922" ht="30" customHeight="1">
@@ -53820,7 +53820,7 @@
       </c>
       <c r="F922" s="1" t="inlineStr">
         <is>
-          <t>develop</t>
+          <t>content</t>
         </is>
       </c>
       <c r="G922" s="1" t="inlineStr">
@@ -53855,7 +53855,7 @@
         <v>921</v>
       </c>
       <c r="N922" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="923" ht="30" customHeight="1">
@@ -53878,7 +53878,7 @@
       </c>
       <c r="F923" s="1" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>feeling</t>
         </is>
       </c>
       <c r="G923" s="1" t="inlineStr">
@@ -53913,7 +53913,7 @@
         <v>922</v>
       </c>
       <c r="N923" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="924" ht="30" customHeight="1">
@@ -53936,7 +53936,7 @@
       </c>
       <c r="F924" s="1" t="inlineStr">
         <is>
-          <t>teen</t>
+          <t>shock</t>
         </is>
       </c>
       <c r="G924" s="1" t="inlineStr">
@@ -53971,7 +53971,7 @@
         <v>923</v>
       </c>
       <c r="N924" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="925" ht="30" customHeight="1">
@@ -53994,7 +53994,7 @@
       </c>
       <c r="F925" s="1" t="inlineStr">
         <is>
-          <t>magazine</t>
+          <t>foreign</t>
         </is>
       </c>
       <c r="G925" s="1" t="inlineStr">
@@ -54029,7 +54029,7 @@
         <v>924</v>
       </c>
       <c r="N925" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="926" ht="30" customHeight="1">
@@ -54052,7 +54052,7 @@
       </c>
       <c r="F926" s="1" t="inlineStr">
         <is>
-          <t>teenager</t>
+          <t>confused</t>
         </is>
       </c>
       <c r="G926" s="1" t="inlineStr">
@@ -54087,7 +54087,7 @@
         <v>925</v>
       </c>
       <c r="N926" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="927" ht="30" customHeight="1">
@@ -54110,7 +54110,7 @@
       </c>
       <c r="F927" s="1" t="inlineStr">
         <is>
-          <t>greeting</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="G927" s="1" t="inlineStr">
@@ -54145,7 +54145,7 @@
         <v>926</v>
       </c>
       <c r="N927" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="928" ht="30" customHeight="1">
@@ -54168,7 +54168,7 @@
       </c>
       <c r="F928" s="1" t="inlineStr">
         <is>
-          <t>grade</t>
+          <t>phase</t>
         </is>
       </c>
       <c r="G928" s="1" t="inlineStr">
@@ -54203,7 +54203,7 @@
         <v>927</v>
       </c>
       <c r="N928" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="929" ht="30" customHeight="1">
@@ -54226,7 +54226,7 @@
       </c>
       <c r="F929" s="1" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>honeymoon</t>
         </is>
       </c>
       <c r="G929" s="1" t="inlineStr">
@@ -54261,7 +54261,7 @@
         <v>928</v>
       </c>
       <c r="N929" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="930" ht="30" customHeight="1">
@@ -54284,7 +54284,7 @@
       </c>
       <c r="F930" s="1" t="inlineStr">
         <is>
-          <t>drama</t>
+          <t>unfamiliar</t>
         </is>
       </c>
       <c r="G930" s="1" t="inlineStr">
@@ -54319,7 +54319,7 @@
         <v>929</v>
       </c>
       <c r="N930" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="931" ht="30" customHeight="1">
@@ -54342,7 +54342,7 @@
       </c>
       <c r="F931" s="1" t="inlineStr">
         <is>
-          <t>sincerely</t>
+          <t>homesick</t>
         </is>
       </c>
       <c r="G931" s="1" t="inlineStr">
@@ -54377,7 +54377,7 @@
         <v>930</v>
       </c>
       <c r="N931" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="932" ht="30" customHeight="1">
@@ -54400,7 +54400,7 @@
       </c>
       <c r="F932" s="1" t="inlineStr">
         <is>
-          <t>diary</t>
+          <t>lonely</t>
         </is>
       </c>
       <c r="G932" s="1" t="inlineStr">
@@ -54435,7 +54435,7 @@
         <v>931</v>
       </c>
       <c r="N932" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="933" ht="30" customHeight="1">
@@ -54458,7 +54458,7 @@
       </c>
       <c r="F933" s="1" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>deal</t>
         </is>
       </c>
       <c r="G933" s="1" t="inlineStr">
@@ -54493,7 +54493,7 @@
         <v>932</v>
       </c>
       <c r="N933" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="934" ht="30" customHeight="1">
@@ -54516,7 +54516,7 @@
       </c>
       <c r="F934" s="1" t="inlineStr">
         <is>
-          <t>poster</t>
+          <t>expect</t>
         </is>
       </c>
       <c r="G934" s="1" t="inlineStr">
@@ -54551,7 +54551,7 @@
         <v>933</v>
       </c>
       <c r="N934" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="935" ht="30" customHeight="1">
@@ -54574,7 +54574,7 @@
       </c>
       <c r="F935" s="1" t="inlineStr">
         <is>
-          <t>realize</t>
+          <t>situation</t>
         </is>
       </c>
       <c r="G935" s="1" t="inlineStr">
@@ -54609,7 +54609,7 @@
         <v>934</v>
       </c>
       <c r="N935" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="936" ht="30" customHeight="1">
@@ -54632,7 +54632,7 @@
       </c>
       <c r="F936" s="1" t="inlineStr">
         <is>
-          <t>luckily</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="G936" s="1" t="inlineStr">
@@ -54667,7 +54667,7 @@
         <v>935</v>
       </c>
       <c r="N936" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="937" ht="30" customHeight="1">
@@ -54690,7 +54690,7 @@
       </c>
       <c r="F937" s="1" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>adaptation</t>
         </is>
       </c>
       <c r="G937" s="1" t="inlineStr">
@@ -54725,7 +54725,7 @@
         <v>936</v>
       </c>
       <c r="N937" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="938" ht="30" customHeight="1">
@@ -54744,11 +54744,11 @@
         <v>6</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F938" s="1" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>beijing opera</t>
         </is>
       </c>
       <c r="G938" s="1" t="inlineStr">
@@ -54806,7 +54806,7 @@
       </c>
       <c r="F939" s="1" t="inlineStr">
         <is>
-          <t>mood</t>
+          <t>host family</t>
         </is>
       </c>
       <c r="G939" s="1" t="inlineStr">
@@ -54841,7 +54841,7 @@
         <v>938</v>
       </c>
       <c r="N939" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="940" ht="30" customHeight="1">
@@ -54864,7 +54864,7 @@
       </c>
       <c r="F940" s="1" t="inlineStr">
         <is>
-          <t>mind</t>
+          <t>snake its way</t>
         </is>
       </c>
       <c r="G940" s="1" t="inlineStr">
@@ -54899,7 +54899,7 @@
         <v>939</v>
       </c>
       <c r="N940" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="941" ht="30" customHeight="1">
@@ -54922,7 +54922,7 @@
       </c>
       <c r="F941" s="1" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>culture shock</t>
         </is>
       </c>
       <c r="G941" s="1" t="inlineStr">
@@ -54957,7 +54957,7 @@
         <v>940</v>
       </c>
       <c r="N941" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="942" ht="30" customHeight="1">
@@ -54980,7 +54980,7 @@
       </c>
       <c r="F942" s="1" t="inlineStr">
         <is>
-          <t>celebrate</t>
+          <t>deal with</t>
         </is>
       </c>
       <c r="G942" s="1" t="inlineStr">
@@ -55015,7 +55015,7 @@
         <v>941</v>
       </c>
       <c r="N942" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="943" ht="30" customHeight="1">
@@ -55038,7 +55038,7 @@
       </c>
       <c r="F943" s="1" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>feel at home</t>
         </is>
       </c>
       <c r="G943" s="1" t="inlineStr">
@@ -55073,7 +55073,7 @@
         <v>942</v>
       </c>
       <c r="N943" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="944" ht="30" customHeight="1">
@@ -55096,7 +55096,7 @@
       </c>
       <c r="F944" s="1" t="inlineStr">
         <is>
-          <t>rocky</t>
+          <t>author</t>
         </is>
       </c>
       <c r="G944" s="1" t="inlineStr">
@@ -55131,7 +55131,7 @@
         <v>943</v>
       </c>
       <c r="N944" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="945" ht="30" customHeight="1">
@@ -55154,7 +55154,7 @@
       </c>
       <c r="F945" s="1" t="inlineStr">
         <is>
-          <t>footprint</t>
+          <t>remains</t>
         </is>
       </c>
       <c r="G945" s="1" t="inlineStr">
@@ -55189,7 +55189,7 @@
         <v>944</v>
       </c>
       <c r="N945" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="946" ht="30" customHeight="1">
@@ -55212,7 +55212,7 @@
       </c>
       <c r="F946" s="1" t="inlineStr">
         <is>
-          <t>wet</t>
+          <t>locate</t>
         </is>
       </c>
       <c r="G946" s="1" t="inlineStr">
@@ -55247,7 +55247,7 @@
         <v>945</v>
       </c>
       <c r="N946" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="947" ht="30" customHeight="1">
@@ -55270,7 +55270,7 @@
       </c>
       <c r="F947" s="1" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>soldier</t>
         </is>
       </c>
       <c r="G947" s="1" t="inlineStr">
@@ -55305,7 +55305,7 @@
         <v>946</v>
       </c>
       <c r="N947" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="948" ht="30" customHeight="1">
@@ -55328,7 +55328,7 @@
       </c>
       <c r="F948" s="1" t="inlineStr">
         <is>
-          <t>sandy</t>
+          <t>captain</t>
         </is>
       </c>
       <c r="G948" s="1" t="inlineStr">
@@ -55363,7 +55363,7 @@
         <v>947</v>
       </c>
       <c r="N948" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="949" ht="30" customHeight="1">
@@ -55386,7 +55386,7 @@
       </c>
       <c r="F949" s="1" t="inlineStr">
         <is>
-          <t>kick</t>
+          <t>empty</t>
         </is>
       </c>
       <c r="G949" s="1" t="inlineStr">
@@ -55421,7 +55421,7 @@
         <v>948</v>
       </c>
       <c r="N949" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="950" ht="30" customHeight="1">
@@ -55444,7 +55444,7 @@
       </c>
       <c r="F950" s="1" t="inlineStr">
         <is>
-          <t>town</t>
+          <t>victory</t>
         </is>
       </c>
       <c r="G950" s="1" t="inlineStr">
@@ -55479,7 +55479,7 @@
         <v>949</v>
       </c>
       <c r="N950" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="951" ht="30" customHeight="1">
@@ -55502,7 +55502,7 @@
       </c>
       <c r="F951" s="1" t="inlineStr">
         <is>
-          <t>feature</t>
+          <t>joke</t>
         </is>
       </c>
       <c r="G951" s="1" t="inlineStr">
@@ -55537,7 +55537,7 @@
         <v>950</v>
       </c>
       <c r="N951" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="952" ht="30" customHeight="1">
@@ -55560,7 +55560,7 @@
       </c>
       <c r="F952" s="1" t="inlineStr">
         <is>
-          <t>south</t>
+          <t>midnight</t>
         </is>
       </c>
       <c r="G952" s="1" t="inlineStr">
@@ -55595,7 +55595,7 @@
         <v>951</v>
       </c>
       <c r="N952" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="953" ht="30" customHeight="1">
@@ -55618,7 +55618,7 @@
       </c>
       <c r="F953" s="1" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>except</t>
         </is>
       </c>
       <c r="G953" s="1" t="inlineStr">
@@ -55653,7 +55653,7 @@
         <v>952</v>
       </c>
       <c r="N953" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="954" ht="30" customHeight="1">
@@ -55676,7 +55676,7 @@
       </c>
       <c r="F954" s="1" t="inlineStr">
         <is>
-          <t>loudly</t>
+          <t>hide</t>
         </is>
       </c>
       <c r="G954" s="1" t="inlineStr">
@@ -55711,7 +55711,7 @@
         <v>953</v>
       </c>
       <c r="N954" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="955" ht="30" customHeight="1">
@@ -55734,7 +55734,7 @@
       </c>
       <c r="F955" s="1" t="inlineStr">
         <is>
-          <t>thunder</t>
+          <t>secretly</t>
         </is>
       </c>
       <c r="G955" s="1" t="inlineStr">
@@ -55769,7 +55769,7 @@
         <v>954</v>
       </c>
       <c r="N955" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="956" ht="30" customHeight="1">
@@ -55792,7 +55792,7 @@
       </c>
       <c r="F956" s="1" t="inlineStr">
         <is>
-          <t>lightning</t>
+          <t>enter</t>
         </is>
       </c>
       <c r="G956" s="1" t="inlineStr">
@@ -55827,7 +55827,7 @@
         <v>955</v>
       </c>
       <c r="N956" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="957" ht="30" customHeight="1">
@@ -55850,7 +55850,7 @@
       </c>
       <c r="F957" s="1" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>succeed</t>
         </is>
       </c>
       <c r="G957" s="1" t="inlineStr">
@@ -55885,7 +55885,7 @@
         <v>956</v>
       </c>
       <c r="N957" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="958" ht="30" customHeight="1">
@@ -55908,7 +55908,7 @@
       </c>
       <c r="F958" s="1" t="inlineStr">
         <is>
-          <t>gather</t>
+          <t>trick</t>
         </is>
       </c>
       <c r="G958" s="1" t="inlineStr">
@@ -55943,7 +55943,7 @@
         <v>957</v>
       </c>
       <c r="N958" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="959" ht="30" customHeight="1">
@@ -55966,7 +55966,7 @@
       </c>
       <c r="F959" s="1" t="inlineStr">
         <is>
-          <t>peaceful</t>
+          <t>fight</t>
         </is>
       </c>
       <c r="G959" s="1" t="inlineStr">
@@ -56001,7 +56001,7 @@
         <v>958</v>
       </c>
       <c r="N959" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="960" ht="30" customHeight="1">
@@ -56024,7 +56024,7 @@
       </c>
       <c r="F960" s="1" t="inlineStr">
         <is>
-          <t>snake</t>
+          <t>beat</t>
         </is>
       </c>
       <c r="G960" s="1" t="inlineStr">
@@ -56059,7 +56059,7 @@
         <v>959</v>
       </c>
       <c r="N960" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="961" ht="30" customHeight="1">
@@ -56082,7 +56082,7 @@
       </c>
       <c r="F961" s="1" t="inlineStr">
         <is>
-          <t>through</t>
+          <t>pretend</t>
         </is>
       </c>
       <c r="G961" s="1" t="inlineStr">
@@ -56117,7 +56117,7 @@
         <v>960</v>
       </c>
       <c r="N961" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="962" ht="30" customHeight="1">
@@ -56140,7 +56140,7 @@
       </c>
       <c r="F962" s="1" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="G962" s="1" t="inlineStr">
@@ -56175,7 +56175,7 @@
         <v>961</v>
       </c>
       <c r="N962" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="963" ht="30" customHeight="1">
@@ -56198,7 +56198,7 @@
       </c>
       <c r="F963" s="1" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="G963" s="1" t="inlineStr">
@@ -56233,7 +56233,7 @@
         <v>962</v>
       </c>
       <c r="N963" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="964" ht="30" customHeight="1">
@@ -56256,7 +56256,7 @@
       </c>
       <c r="F964" s="1" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>therefore</t>
         </is>
       </c>
       <c r="G964" s="1" t="inlineStr">
@@ -56291,7 +56291,7 @@
         <v>963</v>
       </c>
       <c r="N964" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="965" ht="30" customHeight="1">
@@ -56314,7 +56314,7 @@
       </c>
       <c r="F965" s="1" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>within</t>
         </is>
       </c>
       <c r="G965" s="1" t="inlineStr">
@@ -56349,7 +56349,7 @@
         <v>964</v>
       </c>
       <c r="N965" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="966" ht="30" customHeight="1">
@@ -56372,7 +56372,7 @@
       </c>
       <c r="F966" s="1" t="inlineStr">
         <is>
-          <t>sandcastle</t>
+          <t>fill</t>
         </is>
       </c>
       <c r="G966" s="1" t="inlineStr">
@@ -56407,7 +56407,7 @@
         <v>965</v>
       </c>
       <c r="N966" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="967" ht="30" customHeight="1">
@@ -56430,7 +56430,7 @@
       </c>
       <c r="F967" s="1" t="inlineStr">
         <is>
-          <t>follow</t>
+          <t>towards</t>
         </is>
       </c>
       <c r="G967" s="1" t="inlineStr">
@@ -56465,7 +56465,7 @@
         <v>966</v>
       </c>
       <c r="N967" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="968" ht="30" customHeight="1">
@@ -56488,7 +56488,7 @@
       </c>
       <c r="F968" s="1" t="inlineStr">
         <is>
-          <t>divide</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="G968" s="1" t="inlineStr">
@@ -56523,7 +56523,7 @@
         <v>967</v>
       </c>
       <c r="N968" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="969" ht="30" customHeight="1">
@@ -56546,7 +56546,7 @@
       </c>
       <c r="F969" s="1" t="inlineStr">
         <is>
-          <t>decide</t>
+          <t>fog</t>
         </is>
       </c>
       <c r="G969" s="1" t="inlineStr">
@@ -56581,7 +56581,7 @@
         <v>968</v>
       </c>
       <c r="N969" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="970" ht="30" customHeight="1">
@@ -56604,7 +56604,7 @@
       </c>
       <c r="F970" s="1" t="inlineStr">
         <is>
-          <t>crop</t>
+          <t>make jokes about</t>
         </is>
       </c>
       <c r="G970" s="1" t="inlineStr">
@@ -56639,7 +56639,7 @@
         <v>969</v>
       </c>
       <c r="N970" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="971" ht="30" customHeight="1">
@@ -56662,7 +56662,7 @@
       </c>
       <c r="F971" s="1" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>succeed in</t>
         </is>
       </c>
       <c r="G971" s="1" t="inlineStr">
@@ -56697,7 +56697,7 @@
         <v>970</v>
       </c>
       <c r="N971" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="972" ht="30" customHeight="1">
@@ -56720,7 +56720,7 @@
       </c>
       <c r="F972" s="1" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>be tired of</t>
         </is>
       </c>
       <c r="G972" s="1" t="inlineStr">
@@ -56755,7 +56755,7 @@
         <v>971</v>
       </c>
       <c r="N972" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="973" ht="30" customHeight="1">
@@ -56778,7 +56778,7 @@
       </c>
       <c r="F973" s="1" t="inlineStr">
         <is>
-          <t>tradition</t>
+          <t>go on board</t>
         </is>
       </c>
       <c r="G973" s="1" t="inlineStr">
@@ -56813,7 +56813,7 @@
         <v>972</v>
       </c>
       <c r="N973" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="974" ht="30" customHeight="1">
@@ -56836,7 +56836,7 @@
       </c>
       <c r="F974" s="1" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>be jealous of</t>
         </is>
       </c>
       <c r="G974" s="1" t="inlineStr">
@@ -56871,7 +56871,7 @@
         <v>973</v>
       </c>
       <c r="N974" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="975" ht="30" customHeight="1">
@@ -56894,7 +56894,7 @@
       </c>
       <c r="F975" s="1" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>be full of</t>
         </is>
       </c>
       <c r="G975" s="1" t="inlineStr">
@@ -56929,7 +56929,7 @@
         <v>974</v>
       </c>
       <c r="N975" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="976" ht="30" customHeight="1">
@@ -56952,7 +56952,7 @@
       </c>
       <c r="F976" s="1" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="G976" s="1" t="inlineStr">
@@ -56987,7 +56987,7 @@
         <v>975</v>
       </c>
       <c r="N976" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="977" ht="30" customHeight="1">
@@ -57010,7 +57010,7 @@
       </c>
       <c r="F977" s="1" t="inlineStr">
         <is>
-          <t>amazing</t>
+          <t>repeat</t>
         </is>
       </c>
       <c r="G977" s="1" t="inlineStr">
@@ -57045,7 +57045,7 @@
         <v>976</v>
       </c>
       <c r="N977" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="978" ht="30" customHeight="1">
@@ -57068,7 +57068,7 @@
       </c>
       <c r="F978" s="1" t="inlineStr">
         <is>
-          <t>planet</t>
+          <t>note</t>
         </is>
       </c>
       <c r="G978" s="1" t="inlineStr">
@@ -57103,7 +57103,7 @@
         <v>977</v>
       </c>
       <c r="N978" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="979" ht="30" customHeight="1">
@@ -57126,7 +57126,7 @@
       </c>
       <c r="F979" s="1" t="inlineStr">
         <is>
-          <t>billion</t>
+          <t>visual</t>
         </is>
       </c>
       <c r="G979" s="1" t="inlineStr">
@@ -57161,7 +57161,7 @@
         <v>978</v>
       </c>
       <c r="N979" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="980" ht="30" customHeight="1">
@@ -57184,7 +57184,7 @@
       </c>
       <c r="F980" s="1" t="inlineStr">
         <is>
-          <t>cover</t>
+          <t>mentally</t>
         </is>
       </c>
       <c r="G980" s="1" t="inlineStr">
@@ -57219,7 +57219,7 @@
         <v>979</v>
       </c>
       <c r="N980" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="981" ht="30" customHeight="1">
@@ -57242,7 +57242,7 @@
       </c>
       <c r="F981" s="1" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>link</t>
         </is>
       </c>
       <c r="G981" s="1" t="inlineStr">
@@ -57277,7 +57277,7 @@
         <v>980</v>
       </c>
       <c r="N981" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="982" ht="30" customHeight="1">
@@ -57300,7 +57300,7 @@
       </c>
       <c r="F982" s="1" t="inlineStr">
         <is>
-          <t>freezing</t>
+          <t>list</t>
         </is>
       </c>
       <c r="G982" s="1" t="inlineStr">
@@ -57335,7 +57335,7 @@
         <v>981</v>
       </c>
       <c r="N982" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="983" ht="30" customHeight="1">
@@ -57358,7 +57358,7 @@
       </c>
       <c r="F983" s="1" t="inlineStr">
         <is>
-          <t>north</t>
+          <t>especially</t>
         </is>
       </c>
       <c r="G983" s="1" t="inlineStr">
@@ -57393,7 +57393,7 @@
         <v>982</v>
       </c>
       <c r="N983" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="984" ht="30" customHeight="1">
@@ -57416,7 +57416,7 @@
       </c>
       <c r="F984" s="1" t="inlineStr">
         <is>
-          <t>pole</t>
+          <t>diet</t>
         </is>
       </c>
       <c r="G984" s="1" t="inlineStr">
@@ -57451,7 +57451,7 @@
         <v>983</v>
       </c>
       <c r="N984" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="985" ht="30" customHeight="1">
@@ -57474,7 +57474,7 @@
       </c>
       <c r="F985" s="1" t="inlineStr">
         <is>
-          <t>desert</t>
+          <t>maintain</t>
         </is>
       </c>
       <c r="G985" s="1" t="inlineStr">
@@ -57509,7 +57509,7 @@
         <v>984</v>
       </c>
       <c r="N985" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="986" ht="30" customHeight="1">
@@ -57532,7 +57532,7 @@
       </c>
       <c r="F986" s="1" t="inlineStr">
         <is>
-          <t>metre</t>
+          <t>nut</t>
         </is>
       </c>
       <c r="G986" s="1" t="inlineStr">
@@ -57567,7 +57567,7 @@
         <v>985</v>
       </c>
       <c r="N986" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="987" ht="30" customHeight="1">
@@ -57590,7 +57590,7 @@
       </c>
       <c r="F987" s="1" t="inlineStr">
         <is>
-          <t>reach</t>
+          <t>relax</t>
         </is>
       </c>
       <c r="G987" s="1" t="inlineStr">
@@ -57625,7 +57625,7 @@
         <v>986</v>
       </c>
       <c r="N987" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="988" ht="30" customHeight="1">
@@ -57648,7 +57648,7 @@
       </c>
       <c r="F988" s="1" t="inlineStr">
         <is>
-          <t>grain</t>
+          <t>stressed</t>
         </is>
       </c>
       <c r="G988" s="1" t="inlineStr">
@@ -57683,7 +57683,7 @@
         <v>987</v>
       </c>
       <c r="N988" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="989" ht="30" customHeight="1">
@@ -57706,7 +57706,7 @@
       </c>
       <c r="F989" s="1" t="inlineStr">
         <is>
-          <t>wide</t>
+          <t>tend</t>
         </is>
       </c>
       <c r="G989" s="1" t="inlineStr">
@@ -57741,7 +57741,7 @@
         <v>988</v>
       </c>
       <c r="N989" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="990" ht="30" customHeight="1">
@@ -57764,7 +57764,7 @@
       </c>
       <c r="F990" s="1" t="inlineStr">
         <is>
-          <t>whale</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="G990" s="1" t="inlineStr">
@@ -57799,7 +57799,7 @@
         <v>989</v>
       </c>
       <c r="N990" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="991" ht="30" customHeight="1">
@@ -57822,7 +57822,7 @@
       </c>
       <c r="F991" s="1" t="inlineStr">
         <is>
-          <t>butterfly</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="G991" s="1" t="inlineStr">
@@ -57857,7 +57857,7 @@
         <v>990</v>
       </c>
       <c r="N991" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="992" ht="30" customHeight="1">
@@ -57880,7 +57880,7 @@
       </c>
       <c r="F992" s="1" t="inlineStr">
         <is>
-          <t>provide</t>
+          <t>fork</t>
         </is>
       </c>
       <c r="G992" s="1" t="inlineStr">
@@ -57915,7 +57915,7 @@
         <v>991</v>
       </c>
       <c r="N992" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="993" ht="30" customHeight="1">
@@ -57938,7 +57938,7 @@
       </c>
       <c r="F993" s="1" t="inlineStr">
         <is>
-          <t>explore</t>
+          <t>onion</t>
         </is>
       </c>
       <c r="G993" s="1" t="inlineStr">
@@ -57973,7 +57973,7 @@
         <v>992</v>
       </c>
       <c r="N993" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="994" ht="30" customHeight="1">
@@ -57996,7 +57996,7 @@
       </c>
       <c r="F994" s="1" t="inlineStr">
         <is>
-          <t>disappear</t>
+          <t>ant</t>
         </is>
       </c>
       <c r="G994" s="1" t="inlineStr">
@@ -58031,7 +58031,7 @@
         <v>993</v>
       </c>
       <c r="N994" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="995" ht="30" customHeight="1">
@@ -58054,7 +58054,7 @@
       </c>
       <c r="F995" s="1" t="inlineStr">
         <is>
-          <t>plastic</t>
+          <t>context</t>
         </is>
       </c>
       <c r="G995" s="1" t="inlineStr">
@@ -58089,7 +58089,7 @@
         <v>994</v>
       </c>
       <c r="N995" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="996" ht="30" customHeight="1">
@@ -58112,7 +58112,7 @@
       </c>
       <c r="F996" s="1" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>image</t>
         </is>
       </c>
       <c r="G996" s="1" t="inlineStr">
@@ -58147,7 +58147,7 @@
         <v>995</v>
       </c>
       <c r="N996" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="997" ht="30" customHeight="1">
@@ -58170,7 +58170,7 @@
       </c>
       <c r="F997" s="1" t="inlineStr">
         <is>
-          <t>protect</t>
+          <t>sense</t>
         </is>
       </c>
       <c r="G997" s="1" t="inlineStr">
@@ -58205,7 +58205,7 @@
         <v>996</v>
       </c>
       <c r="N997" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="998" ht="30" customHeight="1">
@@ -58228,7 +58228,7 @@
       </c>
       <c r="F998" s="1" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>summary</t>
         </is>
       </c>
       <c r="G998" s="1" t="inlineStr">
@@ -58263,7 +58263,7 @@
         <v>997</v>
       </c>
       <c r="N998" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="999" ht="30" customHeight="1">
@@ -58286,7 +58286,7 @@
       </c>
       <c r="F999" s="1" t="inlineStr">
         <is>
-          <t>groundwater</t>
+          <t>contain</t>
         </is>
       </c>
       <c r="G999" s="1" t="inlineStr">
@@ -58321,7 +58321,7 @@
         <v>998</v>
       </c>
       <c r="N999" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1000" ht="30" customHeight="1">
@@ -58344,7 +58344,7 @@
       </c>
       <c r="F1000" s="1" t="inlineStr">
         <is>
-          <t>burn</t>
+          <t>particular</t>
         </is>
       </c>
       <c r="G1000" s="1" t="inlineStr">
@@ -58379,7 +58379,7 @@
         <v>999</v>
       </c>
       <c r="N1000" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1001" ht="30" customHeight="1">
@@ -58402,7 +58402,7 @@
       </c>
       <c r="F1001" s="1" t="inlineStr">
         <is>
-          <t>oil</t>
+          <t>chemistry</t>
         </is>
       </c>
       <c r="G1001" s="1" t="inlineStr">
@@ -58437,7 +58437,7 @@
         <v>1000</v>
       </c>
       <c r="N1001" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1002" ht="30" customHeight="1">
@@ -58460,7 +58460,7 @@
       </c>
       <c r="F1002" s="1" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>flash card</t>
         </is>
       </c>
       <c r="G1002" s="1" t="inlineStr">
@@ -58495,7 +58495,7 @@
         <v>1001</v>
       </c>
       <c r="N1002" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
